--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" tabRatio="672" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" tabRatio="672" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Сводная" sheetId="5" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Июль 2026" sheetId="8" r:id="rId7"/>
     <sheet name="Август 2026" sheetId="9" r:id="rId8"/>
     <sheet name="Сентябрь 2026" sheetId="10" r:id="rId9"/>
+    <sheet name="Октябрь 2026" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -7350,8 +7351,494 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>SABEN_MUSIC</author>
+  </authors>
+  <commentList>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Вторая часть поездки в СПБ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Умами</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Вк музыка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Метро</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Перевел вместе с деньгами за Умами
++
+Подарок в золотом яблоке</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Вернул долг бате</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Соул бейби - завтрак,
+Итали - ужин</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Суверниры родителям из СПБ
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарок маме на ДР</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Метро</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Перевел 4500 в начале дня, не помню на что
++
+первый платеж за серьги и браслет (подарок на др)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z5" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Кунтскамера</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I6" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Завтрак в астер</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q6" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Чаевые дворецкому</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X6" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Книги в буквоеде</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Аптека</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC7" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама перевела на бенз</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X9" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>SABEN_MUSIC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Озон
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="92">
   <si>
     <t>Месяц</t>
   </si>
@@ -7655,16 +8142,19 @@
   <si>
     <t>Перекресток / Метро / Глобус</t>
   </si>
+  <si>
+    <t>Доходы - Расходы Октябрь 2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="#\ ##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="164" formatCode="#\ ##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="55">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8005,8 +8495,29 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Algerian"/>
+      <family val="5"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8226,6 +8737,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCC4C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8705,7 +9222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8741,67 +9258,67 @@
     <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="13" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="16" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="15" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8829,148 +9346,148 @@
     <xf numFmtId="0" fontId="11" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="22" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="22" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="23" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="23" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="15" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="15" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="26" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="26" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="28" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="22" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="28" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="22" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="16" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="24" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="30" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="27" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="29" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="27" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="29" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="30" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="30" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="30" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="31" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="30" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="31" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="30" fillId="31" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="30" fillId="31" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="32" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="29" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="29" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="35" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8979,56 +9496,56 @@
     <xf numFmtId="0" fontId="34" fillId="29" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="35" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="36" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="37" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="29" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="36" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="35" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="38" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="37" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="37" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="36" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="38" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="35" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="37" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="36" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="36" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="36" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="36" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
@@ -9036,15 +9553,103 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="41" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="41" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="41" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="40" fillId="31" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="41" fillId="31" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="41" fillId="31" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="41" fillId="31" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="41" fillId="31" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="23" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="23" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="23" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="37" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="37" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="37" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="37" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="37" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="37" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="37" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="37" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="51" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9084,19 +9689,34 @@
     <xf numFmtId="0" fontId="24" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -9120,24 +9740,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -9147,126 +9749,112 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="37" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="52" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="52" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="38" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="23" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="52" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="23" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="52" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="52" fillId="23" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="23" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="23" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="23" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="23" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="37" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="37" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="37" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="37" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="52" fillId="37" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="37" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="37" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="37" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="37" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="11" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="16" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="51" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color rgb="FF57B418"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF57B418"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF57B418"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF57B418"/>
@@ -9311,9 +9899,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFA8A8A"/>
       <color rgb="FFFCC4C4"/>
       <color rgb="FFFDD7D7"/>
+      <color rgb="FFFA8A8A"/>
       <color rgb="FF183C5C"/>
       <color rgb="FFDDF0C8"/>
       <color rgb="FF273C18"/>
@@ -9871,23 +10459,2017 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H17">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>H17&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>H17&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H16">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>H5&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>H5&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AZ41"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="25" width="20.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="23.140625" style="1" customWidth="1"/>
+    <col min="27" max="30" width="20.7109375" style="1" customWidth="1"/>
+    <col min="31" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="38" width="19" style="1" customWidth="1"/>
+    <col min="39" max="42" width="12.7109375" style="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:52" ht="34.5" customHeight="1">
+      <c r="A1" s="194" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="194"/>
+      <c r="I1" s="194"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="194"/>
+      <c r="Y1" s="194"/>
+      <c r="Z1" s="194"/>
+      <c r="AA1" s="194"/>
+      <c r="AB1" s="194"/>
+      <c r="AC1" s="194"/>
+      <c r="AD1" s="194"/>
+    </row>
+    <row r="2" spans="1:52" ht="26.25">
+      <c r="A2" s="195"/>
+      <c r="B2" s="196"/>
+      <c r="C2" s="197" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="198" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="198"/>
+      <c r="N2" s="198"/>
+      <c r="O2" s="198"/>
+      <c r="P2" s="198"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="199" t="s">
+        <v>69</v>
+      </c>
+      <c r="S2" s="199"/>
+      <c r="T2" s="199"/>
+      <c r="U2" s="199"/>
+      <c r="V2" s="199"/>
+      <c r="W2" s="199"/>
+      <c r="X2" s="199"/>
+      <c r="Y2" s="199"/>
+      <c r="Z2" s="199"/>
+      <c r="AA2" s="199"/>
+      <c r="AB2" s="200" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC2" s="200"/>
+      <c r="AD2" s="200"/>
+    </row>
+    <row r="3" spans="1:52" ht="45" customHeight="1" thickBot="1">
+      <c r="A3" s="221" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="221" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="222" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="222" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="222" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="222" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="222" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="222" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="222" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="222" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="223" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="223" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="223" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="223" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="223" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" s="223" t="s">
+        <v>80</v>
+      </c>
+      <c r="R3" s="224" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="224" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" s="224" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" s="224" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" s="224" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" s="224" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" s="224" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y3" s="224" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z3" s="224" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA3" s="225" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD3" s="206" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="10"/>
+      <c r="AL3" s="10"/>
+      <c r="AM3" s="10"/>
+      <c r="AN3" s="10"/>
+      <c r="AO3" s="10"/>
+      <c r="AP3" s="10"/>
+      <c r="AQ3" s="10"/>
+      <c r="AR3" s="10"/>
+      <c r="AS3" s="10"/>
+      <c r="AT3" s="10"/>
+      <c r="AU3" s="10"/>
+      <c r="AV3" s="10"/>
+      <c r="AW3" s="10"/>
+      <c r="AX3" s="10"/>
+      <c r="AY3" s="10"/>
+      <c r="AZ3" s="10"/>
+    </row>
+    <row r="4" spans="1:52" ht="15.75">
+      <c r="A4" s="150">
+        <v>5</v>
+      </c>
+      <c r="B4" s="151" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="230"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="230">
+        <v>300.95999999999998</v>
+      </c>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
+      <c r="H4" s="230"/>
+      <c r="I4" s="230">
+        <f>5000+415.8</f>
+        <v>5415.8</v>
+      </c>
+      <c r="J4" s="230"/>
+      <c r="K4" s="230"/>
+      <c r="L4" s="230"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230">
+        <v>199</v>
+      </c>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230">
+        <f>190+190</f>
+        <v>380</v>
+      </c>
+      <c r="V4" s="230"/>
+      <c r="W4" s="230">
+        <f>1000+3865</f>
+        <v>4865</v>
+      </c>
+      <c r="X4" s="230">
+        <v>20000</v>
+      </c>
+      <c r="Y4" s="230"/>
+      <c r="Z4" s="230"/>
+      <c r="AA4" s="231"/>
+      <c r="AB4" s="211">
+        <f>SUM(C4:AA4)</f>
+        <v>31160.760000000002</v>
+      </c>
+      <c r="AC4" s="166">
+        <v>142200.85999999999</v>
+      </c>
+      <c r="AD4" s="192"/>
+    </row>
+    <row r="5" spans="1:52" ht="15.75">
+      <c r="A5" s="236">
+        <v>6</v>
+      </c>
+      <c r="B5" s="212" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="237"/>
+      <c r="D5" s="237"/>
+      <c r="E5" s="237"/>
+      <c r="F5" s="237"/>
+      <c r="G5" s="237"/>
+      <c r="H5" s="237"/>
+      <c r="I5" s="237">
+        <f>5020+655+6960+1134</f>
+        <v>13769</v>
+      </c>
+      <c r="J5" s="237"/>
+      <c r="K5" s="237"/>
+      <c r="L5" s="237"/>
+      <c r="M5" s="237"/>
+      <c r="N5" s="237"/>
+      <c r="O5" s="237">
+        <f>1930+3470</f>
+        <v>5400</v>
+      </c>
+      <c r="P5" s="237">
+        <v>11093</v>
+      </c>
+      <c r="Q5" s="237"/>
+      <c r="R5" s="237"/>
+      <c r="S5" s="237"/>
+      <c r="T5" s="237"/>
+      <c r="U5" s="237">
+        <f>190+190</f>
+        <v>380</v>
+      </c>
+      <c r="V5" s="237"/>
+      <c r="W5" s="237">
+        <f>4500+11525</f>
+        <v>16025</v>
+      </c>
+      <c r="X5" s="237"/>
+      <c r="Y5" s="237"/>
+      <c r="Z5" s="237">
+        <f>1000</f>
+        <v>1000</v>
+      </c>
+      <c r="AA5" s="238"/>
+      <c r="AB5" s="211">
+        <f>SUM(C5:AA5)</f>
+        <v>47667</v>
+      </c>
+      <c r="AC5" s="168"/>
+      <c r="AD5" s="192"/>
+    </row>
+    <row r="6" spans="1:52" ht="16.5" thickBot="1">
+      <c r="A6" s="234">
+        <v>7</v>
+      </c>
+      <c r="B6" s="235" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="232"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="232"/>
+      <c r="G6" s="232"/>
+      <c r="H6" s="232"/>
+      <c r="I6" s="232">
+        <f>4210+461</f>
+        <v>4671</v>
+      </c>
+      <c r="J6" s="232">
+        <f>290</f>
+        <v>290</v>
+      </c>
+      <c r="K6" s="232"/>
+      <c r="L6" s="232"/>
+      <c r="M6" s="232"/>
+      <c r="N6" s="232"/>
+      <c r="O6" s="232"/>
+      <c r="P6" s="232"/>
+      <c r="Q6" s="232">
+        <f>300</f>
+        <v>300</v>
+      </c>
+      <c r="R6" s="232"/>
+      <c r="S6" s="232"/>
+      <c r="T6" s="232"/>
+      <c r="U6" s="232">
+        <f>391</f>
+        <v>391</v>
+      </c>
+      <c r="V6" s="232"/>
+      <c r="W6" s="232"/>
+      <c r="X6" s="232">
+        <f>3807</f>
+        <v>3807</v>
+      </c>
+      <c r="Y6" s="232"/>
+      <c r="Z6" s="232"/>
+      <c r="AA6" s="233"/>
+      <c r="AB6" s="211">
+        <f t="shared" ref="AB6:AB16" si="0">SUM(C6:AA6)</f>
+        <v>9459</v>
+      </c>
+      <c r="AC6" s="168"/>
+      <c r="AD6" s="192"/>
+    </row>
+    <row r="7" spans="1:52" ht="15.75">
+      <c r="A7" s="226">
+        <v>8</v>
+      </c>
+      <c r="B7" s="227" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="228">
+        <f>273.98</f>
+        <v>273.98</v>
+      </c>
+      <c r="D7" s="228">
+        <f>556.94</f>
+        <v>556.94000000000005</v>
+      </c>
+      <c r="E7" s="228"/>
+      <c r="F7" s="228"/>
+      <c r="G7" s="228"/>
+      <c r="H7" s="228"/>
+      <c r="I7" s="228"/>
+      <c r="J7" s="228"/>
+      <c r="K7" s="228"/>
+      <c r="L7" s="228"/>
+      <c r="M7" s="228">
+        <f>2001+69</f>
+        <v>2070</v>
+      </c>
+      <c r="N7" s="228"/>
+      <c r="O7" s="228"/>
+      <c r="P7" s="228"/>
+      <c r="Q7" s="228"/>
+      <c r="R7" s="228"/>
+      <c r="S7" s="228"/>
+      <c r="T7" s="228"/>
+      <c r="U7" s="228">
+        <f>182</f>
+        <v>182</v>
+      </c>
+      <c r="V7" s="228"/>
+      <c r="W7" s="228"/>
+      <c r="X7" s="228"/>
+      <c r="Y7" s="228"/>
+      <c r="Z7" s="228"/>
+      <c r="AA7" s="229"/>
+      <c r="AB7" s="15">
+        <f t="shared" si="0"/>
+        <v>3082.92</v>
+      </c>
+      <c r="AC7" s="168">
+        <v>2000</v>
+      </c>
+      <c r="AD7" s="192"/>
+    </row>
+    <row r="8" spans="1:52" ht="15" customHeight="1">
+      <c r="A8" s="11">
+        <v>9</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="213"/>
+      <c r="D8" s="213"/>
+      <c r="E8" s="213"/>
+      <c r="F8" s="213">
+        <f>2946.51</f>
+        <v>2946.51</v>
+      </c>
+      <c r="G8" s="213"/>
+      <c r="H8" s="213"/>
+      <c r="I8" s="213"/>
+      <c r="J8" s="213"/>
+      <c r="K8" s="213"/>
+      <c r="L8" s="213"/>
+      <c r="M8" s="213"/>
+      <c r="N8" s="213"/>
+      <c r="O8" s="213"/>
+      <c r="P8" s="213"/>
+      <c r="Q8" s="213"/>
+      <c r="R8" s="213"/>
+      <c r="S8" s="213"/>
+      <c r="T8" s="213"/>
+      <c r="U8" s="213"/>
+      <c r="V8" s="213"/>
+      <c r="W8" s="213"/>
+      <c r="X8" s="213"/>
+      <c r="Y8" s="213"/>
+      <c r="Z8" s="213"/>
+      <c r="AA8" s="214"/>
+      <c r="AB8" s="15">
+        <f t="shared" si="0"/>
+        <v>2946.51</v>
+      </c>
+      <c r="AC8" s="168"/>
+      <c r="AD8" s="192"/>
+    </row>
+    <row r="9" spans="1:52" ht="15.75">
+      <c r="A9" s="17">
+        <v>10</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="215">
+        <f>1177.84</f>
+        <v>1177.8399999999999</v>
+      </c>
+      <c r="D9" s="215"/>
+      <c r="E9" s="215"/>
+      <c r="F9" s="215"/>
+      <c r="G9" s="215"/>
+      <c r="H9" s="215"/>
+      <c r="I9" s="215"/>
+      <c r="J9" s="215"/>
+      <c r="K9" s="215"/>
+      <c r="L9" s="215"/>
+      <c r="M9" s="215"/>
+      <c r="N9" s="215"/>
+      <c r="O9" s="215"/>
+      <c r="P9" s="215"/>
+      <c r="Q9" s="215"/>
+      <c r="R9" s="215"/>
+      <c r="S9" s="215"/>
+      <c r="T9" s="215"/>
+      <c r="U9" s="215"/>
+      <c r="V9" s="215"/>
+      <c r="W9" s="215"/>
+      <c r="X9" s="215">
+        <f>500</f>
+        <v>500</v>
+      </c>
+      <c r="Y9" s="215"/>
+      <c r="Z9" s="215"/>
+      <c r="AA9" s="216"/>
+      <c r="AB9" s="15">
+        <f t="shared" si="0"/>
+        <v>1677.84</v>
+      </c>
+      <c r="AC9" s="168"/>
+      <c r="AD9" s="192"/>
+    </row>
+    <row r="10" spans="1:52" ht="15.75">
+      <c r="A10" s="11">
+        <v>11</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="213"/>
+      <c r="D10" s="213"/>
+      <c r="E10" s="213"/>
+      <c r="F10" s="213">
+        <f>1640</f>
+        <v>1640</v>
+      </c>
+      <c r="G10" s="213"/>
+      <c r="H10" s="213"/>
+      <c r="I10" s="213"/>
+      <c r="J10" s="213"/>
+      <c r="K10" s="213"/>
+      <c r="L10" s="213"/>
+      <c r="M10" s="213"/>
+      <c r="N10" s="213"/>
+      <c r="O10" s="213"/>
+      <c r="P10" s="213"/>
+      <c r="Q10" s="213"/>
+      <c r="R10" s="213"/>
+      <c r="S10" s="213"/>
+      <c r="T10" s="213"/>
+      <c r="U10" s="213"/>
+      <c r="V10" s="213"/>
+      <c r="W10" s="213"/>
+      <c r="X10" s="213"/>
+      <c r="Y10" s="213"/>
+      <c r="Z10" s="213"/>
+      <c r="AA10" s="214"/>
+      <c r="AB10" s="15">
+        <f t="shared" si="0"/>
+        <v>1640</v>
+      </c>
+      <c r="AC10" s="168"/>
+      <c r="AD10" s="192"/>
+    </row>
+    <row r="11" spans="1:52" ht="15.75">
+      <c r="A11" s="17">
+        <v>12</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="215"/>
+      <c r="D11" s="215"/>
+      <c r="E11" s="215"/>
+      <c r="F11" s="215"/>
+      <c r="G11" s="215"/>
+      <c r="H11" s="215"/>
+      <c r="I11" s="215"/>
+      <c r="J11" s="215"/>
+      <c r="K11" s="215"/>
+      <c r="L11" s="215"/>
+      <c r="M11" s="215"/>
+      <c r="N11" s="215"/>
+      <c r="O11" s="215"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="215"/>
+      <c r="S11" s="215"/>
+      <c r="T11" s="215"/>
+      <c r="U11" s="215"/>
+      <c r="V11" s="215"/>
+      <c r="W11" s="215"/>
+      <c r="X11" s="215"/>
+      <c r="Y11" s="215"/>
+      <c r="Z11" s="215"/>
+      <c r="AA11" s="216"/>
+      <c r="AB11" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="168"/>
+      <c r="AD11" s="192"/>
+      <c r="AH11" s="193" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI11" s="193"/>
+      <c r="AJ11" s="193"/>
+      <c r="AK11" s="193"/>
+      <c r="AL11" s="193"/>
+    </row>
+    <row r="12" spans="1:52" ht="15.75">
+      <c r="A12" s="11">
+        <v>13</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="213"/>
+      <c r="D12" s="213"/>
+      <c r="E12" s="213"/>
+      <c r="F12" s="213"/>
+      <c r="G12" s="213"/>
+      <c r="H12" s="213"/>
+      <c r="I12" s="213"/>
+      <c r="J12" s="213"/>
+      <c r="K12" s="213"/>
+      <c r="L12" s="213"/>
+      <c r="M12" s="213"/>
+      <c r="N12" s="213"/>
+      <c r="O12" s="213"/>
+      <c r="P12" s="213"/>
+      <c r="Q12" s="213"/>
+      <c r="R12" s="213"/>
+      <c r="S12" s="213"/>
+      <c r="T12" s="213"/>
+      <c r="U12" s="213"/>
+      <c r="V12" s="213"/>
+      <c r="W12" s="213"/>
+      <c r="X12" s="213"/>
+      <c r="Y12" s="213"/>
+      <c r="Z12" s="213"/>
+      <c r="AA12" s="214"/>
+      <c r="AB12" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC12" s="168"/>
+      <c r="AD12" s="192"/>
+      <c r="AH12" s="193"/>
+      <c r="AI12" s="193"/>
+      <c r="AJ12" s="193"/>
+      <c r="AK12" s="193"/>
+      <c r="AL12" s="193"/>
+    </row>
+    <row r="13" spans="1:52" ht="15.75">
+      <c r="A13" s="17">
+        <v>14</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="215"/>
+      <c r="D13" s="215"/>
+      <c r="E13" s="215"/>
+      <c r="F13" s="215"/>
+      <c r="G13" s="215"/>
+      <c r="H13" s="215"/>
+      <c r="I13" s="215"/>
+      <c r="J13" s="215"/>
+      <c r="K13" s="215"/>
+      <c r="L13" s="215"/>
+      <c r="M13" s="215"/>
+      <c r="N13" s="215"/>
+      <c r="O13" s="215"/>
+      <c r="P13" s="215"/>
+      <c r="Q13" s="215"/>
+      <c r="R13" s="215"/>
+      <c r="S13" s="215"/>
+      <c r="T13" s="215"/>
+      <c r="U13" s="215"/>
+      <c r="V13" s="215"/>
+      <c r="W13" s="215"/>
+      <c r="X13" s="215"/>
+      <c r="Y13" s="215"/>
+      <c r="Z13" s="215"/>
+      <c r="AA13" s="216"/>
+      <c r="AB13" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="168"/>
+      <c r="AD13" s="192"/>
+      <c r="AH13" s="193"/>
+      <c r="AI13" s="193"/>
+      <c r="AJ13" s="193"/>
+      <c r="AK13" s="193"/>
+      <c r="AL13" s="193"/>
+    </row>
+    <row r="14" spans="1:52" ht="18">
+      <c r="A14" s="11">
+        <v>15</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="213"/>
+      <c r="D14" s="213"/>
+      <c r="E14" s="213"/>
+      <c r="F14" s="213"/>
+      <c r="G14" s="213"/>
+      <c r="H14" s="213"/>
+      <c r="I14" s="213"/>
+      <c r="J14" s="213"/>
+      <c r="K14" s="213"/>
+      <c r="L14" s="213"/>
+      <c r="M14" s="213"/>
+      <c r="N14" s="213"/>
+      <c r="O14" s="213"/>
+      <c r="P14" s="213"/>
+      <c r="Q14" s="213"/>
+      <c r="R14" s="213"/>
+      <c r="S14" s="213"/>
+      <c r="T14" s="213"/>
+      <c r="U14" s="213"/>
+      <c r="V14" s="213"/>
+      <c r="W14" s="213"/>
+      <c r="X14" s="213"/>
+      <c r="Y14" s="213"/>
+      <c r="Z14" s="213"/>
+      <c r="AA14" s="214"/>
+      <c r="AB14" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="168"/>
+      <c r="AD14" s="192"/>
+      <c r="AH14" s="189" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI14" s="189"/>
+      <c r="AJ14" s="189"/>
+      <c r="AK14" s="189"/>
+      <c r="AL14" s="22">
+        <f>AC4+AC20+AC24+AC10</f>
+        <v>142200.85999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:52" ht="18">
+      <c r="A15" s="17">
+        <v>16</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="215"/>
+      <c r="D15" s="215"/>
+      <c r="E15" s="215"/>
+      <c r="F15" s="215"/>
+      <c r="G15" s="215"/>
+      <c r="H15" s="215"/>
+      <c r="I15" s="215"/>
+      <c r="J15" s="215"/>
+      <c r="K15" s="215"/>
+      <c r="L15" s="215"/>
+      <c r="M15" s="215"/>
+      <c r="N15" s="215"/>
+      <c r="O15" s="215"/>
+      <c r="P15" s="215"/>
+      <c r="Q15" s="215"/>
+      <c r="R15" s="215"/>
+      <c r="S15" s="215"/>
+      <c r="T15" s="215"/>
+      <c r="U15" s="215"/>
+      <c r="V15" s="215"/>
+      <c r="W15" s="215"/>
+      <c r="X15" s="215"/>
+      <c r="Y15" s="215"/>
+      <c r="Z15" s="215"/>
+      <c r="AA15" s="216"/>
+      <c r="AB15" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="166"/>
+      <c r="AD15" s="192"/>
+      <c r="AH15" s="189" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI15" s="189"/>
+      <c r="AJ15" s="189"/>
+      <c r="AK15" s="189"/>
+      <c r="AL15" s="22">
+        <f>AC21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:52" ht="18">
+      <c r="A16" s="11">
+        <v>17</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="213"/>
+      <c r="D16" s="213"/>
+      <c r="E16" s="213"/>
+      <c r="F16" s="213"/>
+      <c r="G16" s="213"/>
+      <c r="H16" s="213"/>
+      <c r="I16" s="213"/>
+      <c r="J16" s="213"/>
+      <c r="K16" s="213"/>
+      <c r="L16" s="213"/>
+      <c r="M16" s="213"/>
+      <c r="N16" s="213"/>
+      <c r="O16" s="213"/>
+      <c r="P16" s="213"/>
+      <c r="Q16" s="213"/>
+      <c r="R16" s="213"/>
+      <c r="S16" s="213"/>
+      <c r="T16" s="213"/>
+      <c r="U16" s="213"/>
+      <c r="V16" s="213"/>
+      <c r="W16" s="213"/>
+      <c r="X16" s="213"/>
+      <c r="Y16" s="213"/>
+      <c r="Z16" s="213"/>
+      <c r="AA16" s="214"/>
+      <c r="AB16" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="166"/>
+      <c r="AD16" s="192"/>
+      <c r="AH16" s="189" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI16" s="189"/>
+      <c r="AJ16" s="189"/>
+      <c r="AK16" s="189"/>
+      <c r="AL16" s="22" t="e">
+        <f>AC16+AC29+AC35+#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" ht="18">
+      <c r="A17" s="17">
+        <v>18</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="215"/>
+      <c r="D17" s="215"/>
+      <c r="E17" s="215"/>
+      <c r="F17" s="215"/>
+      <c r="G17" s="215"/>
+      <c r="H17" s="215"/>
+      <c r="I17" s="215"/>
+      <c r="J17" s="215"/>
+      <c r="K17" s="215"/>
+      <c r="L17" s="215"/>
+      <c r="M17" s="215"/>
+      <c r="N17" s="215"/>
+      <c r="O17" s="215"/>
+      <c r="P17" s="215"/>
+      <c r="Q17" s="215"/>
+      <c r="R17" s="215"/>
+      <c r="S17" s="215"/>
+      <c r="T17" s="215"/>
+      <c r="U17" s="215"/>
+      <c r="V17" s="215"/>
+      <c r="W17" s="215"/>
+      <c r="X17" s="215"/>
+      <c r="Y17" s="215"/>
+      <c r="Z17" s="215"/>
+      <c r="AA17" s="216"/>
+      <c r="AB17" s="15">
+        <f>SUM(C17:AA17)</f>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="166"/>
+      <c r="AD17" s="192"/>
+      <c r="AH17" s="201" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI17" s="202"/>
+      <c r="AJ17" s="202"/>
+      <c r="AK17" s="203"/>
+      <c r="AL17" s="22">
+        <f>SUM(C37:K37)</f>
+        <v>31042.03</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" ht="18">
+      <c r="A18" s="11">
+        <v>19</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="213"/>
+      <c r="D18" s="213"/>
+      <c r="E18" s="213"/>
+      <c r="F18" s="213"/>
+      <c r="G18" s="213"/>
+      <c r="H18" s="213"/>
+      <c r="I18" s="213"/>
+      <c r="J18" s="213"/>
+      <c r="K18" s="213"/>
+      <c r="L18" s="213"/>
+      <c r="M18" s="213"/>
+      <c r="N18" s="213"/>
+      <c r="O18" s="213"/>
+      <c r="P18" s="213"/>
+      <c r="Q18" s="213"/>
+      <c r="R18" s="213"/>
+      <c r="S18" s="213"/>
+      <c r="T18" s="213"/>
+      <c r="U18" s="213"/>
+      <c r="V18" s="213"/>
+      <c r="W18" s="213"/>
+      <c r="X18" s="213"/>
+      <c r="Y18" s="213"/>
+      <c r="Z18" s="213"/>
+      <c r="AA18" s="214"/>
+      <c r="AB18" s="15">
+        <f>SUM(C18:AA18)</f>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="166"/>
+      <c r="AD18" s="192"/>
+      <c r="AH18" s="139"/>
+      <c r="AI18" s="140"/>
+      <c r="AJ18" s="140"/>
+      <c r="AK18" s="141"/>
+      <c r="AL18" s="22"/>
+    </row>
+    <row r="19" spans="1:38" ht="19.5" customHeight="1">
+      <c r="A19" s="205" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="205"/>
+      <c r="C19" s="23">
+        <f>SUM(C4:C18)</f>
+        <v>1451.82</v>
+      </c>
+      <c r="D19" s="23">
+        <f t="shared" ref="D19:K19" si="1">SUM(D4:D18)</f>
+        <v>556.94000000000005</v>
+      </c>
+      <c r="E19" s="23">
+        <f t="shared" si="1"/>
+        <v>300.95999999999998</v>
+      </c>
+      <c r="F19" s="23">
+        <f t="shared" si="1"/>
+        <v>4586.51</v>
+      </c>
+      <c r="G19" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="1"/>
+        <v>23855.8</v>
+      </c>
+      <c r="J19" s="23">
+        <f t="shared" si="1"/>
+        <v>290</v>
+      </c>
+      <c r="K19" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="24">
+        <f>SUM(L5:L18)</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="24">
+        <f t="shared" ref="M19:Q19" si="2">SUM(M5:M18)</f>
+        <v>2070</v>
+      </c>
+      <c r="N19" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="24">
+        <f t="shared" si="2"/>
+        <v>5400</v>
+      </c>
+      <c r="P19" s="24">
+        <f t="shared" si="2"/>
+        <v>11093</v>
+      </c>
+      <c r="Q19" s="24">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="R19" s="25">
+        <f>SUM(R4:R18)</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="25">
+        <f t="shared" ref="S19:AA19" si="3">SUM(S4:S18)</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="25">
+        <f t="shared" si="3"/>
+        <v>1333</v>
+      </c>
+      <c r="V19" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="25">
+        <f t="shared" si="3"/>
+        <v>20890</v>
+      </c>
+      <c r="X19" s="25">
+        <f t="shared" si="3"/>
+        <v>24307</v>
+      </c>
+      <c r="Y19" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="25">
+        <f t="shared" si="3"/>
+        <v>1000</v>
+      </c>
+      <c r="AA19" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="26">
+        <f>SUM(AB4:AB18)</f>
+        <v>97634.03</v>
+      </c>
+      <c r="AC19" s="27">
+        <f t="shared" ref="AC19" si="4">SUM(AC4:AC17)</f>
+        <v>144200.85999999999</v>
+      </c>
+      <c r="AD19" s="167">
+        <f>AC19-AB19</f>
+        <v>46566.829999999987</v>
+      </c>
+      <c r="AH19" s="189" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI19" s="189"/>
+      <c r="AJ19" s="189"/>
+      <c r="AK19" s="189"/>
+      <c r="AL19" s="22">
+        <f>SUM(L37:Q37)</f>
+        <v>18863</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" ht="18">
+      <c r="A20" s="11">
+        <v>20</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="213"/>
+      <c r="D20" s="213"/>
+      <c r="E20" s="213"/>
+      <c r="F20" s="213"/>
+      <c r="G20" s="213"/>
+      <c r="H20" s="213"/>
+      <c r="I20" s="213"/>
+      <c r="J20" s="213"/>
+      <c r="K20" s="213"/>
+      <c r="L20" s="213"/>
+      <c r="M20" s="213"/>
+      <c r="N20" s="213"/>
+      <c r="O20" s="213"/>
+      <c r="P20" s="213"/>
+      <c r="Q20" s="213"/>
+      <c r="R20" s="213"/>
+      <c r="S20" s="213"/>
+      <c r="T20" s="213"/>
+      <c r="U20" s="213"/>
+      <c r="V20" s="213"/>
+      <c r="W20" s="213"/>
+      <c r="X20" s="213"/>
+      <c r="Y20" s="213"/>
+      <c r="Z20" s="213"/>
+      <c r="AA20" s="214"/>
+      <c r="AB20" s="15">
+        <f>SUM(C20:AA20)</f>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="192"/>
+      <c r="AH20" s="189" t="s">
+        <v>85</v>
+      </c>
+      <c r="AI20" s="189"/>
+      <c r="AJ20" s="189"/>
+      <c r="AK20" s="189"/>
+      <c r="AL20" s="22">
+        <f>W37</f>
+        <v>20890</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" ht="18">
+      <c r="A21" s="17">
+        <v>21</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="215"/>
+      <c r="D21" s="215"/>
+      <c r="E21" s="215"/>
+      <c r="F21" s="215"/>
+      <c r="G21" s="215"/>
+      <c r="H21" s="215"/>
+      <c r="I21" s="215"/>
+      <c r="J21" s="215"/>
+      <c r="K21" s="215"/>
+      <c r="L21" s="215"/>
+      <c r="M21" s="215"/>
+      <c r="N21" s="215"/>
+      <c r="O21" s="215"/>
+      <c r="P21" s="215"/>
+      <c r="Q21" s="215"/>
+      <c r="R21" s="215"/>
+      <c r="S21" s="215"/>
+      <c r="T21" s="215"/>
+      <c r="U21" s="215"/>
+      <c r="V21" s="215"/>
+      <c r="W21" s="215"/>
+      <c r="X21" s="215"/>
+      <c r="Y21" s="215"/>
+      <c r="Z21" s="215"/>
+      <c r="AA21" s="216"/>
+      <c r="AB21" s="15">
+        <f>SUM(C21:AA21)</f>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="21"/>
+      <c r="AD21" s="192"/>
+      <c r="AF21" s="29"/>
+      <c r="AH21" s="189" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI21" s="189"/>
+      <c r="AJ21" s="189"/>
+      <c r="AK21" s="189"/>
+      <c r="AL21" s="22">
+        <f>SUM(U37:V37)</f>
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" ht="18">
+      <c r="A22" s="11">
+        <v>22</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="213"/>
+      <c r="D22" s="213"/>
+      <c r="E22" s="213"/>
+      <c r="F22" s="213"/>
+      <c r="G22" s="213"/>
+      <c r="H22" s="213"/>
+      <c r="I22" s="213"/>
+      <c r="J22" s="213"/>
+      <c r="K22" s="213"/>
+      <c r="L22" s="213"/>
+      <c r="M22" s="213"/>
+      <c r="N22" s="213"/>
+      <c r="O22" s="213"/>
+      <c r="P22" s="213"/>
+      <c r="Q22" s="213"/>
+      <c r="R22" s="213"/>
+      <c r="S22" s="213"/>
+      <c r="T22" s="213"/>
+      <c r="U22" s="213"/>
+      <c r="V22" s="213"/>
+      <c r="W22" s="213"/>
+      <c r="X22" s="213"/>
+      <c r="Y22" s="213"/>
+      <c r="Z22" s="213"/>
+      <c r="AA22" s="214"/>
+      <c r="AB22" s="15">
+        <f t="shared" ref="AB22:AB31" si="5">SUM(C22:AA22)</f>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="21"/>
+      <c r="AD22" s="192"/>
+      <c r="AH22" s="207" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI22" s="207"/>
+      <c r="AJ22" s="207"/>
+      <c r="AK22" s="207"/>
+      <c r="AL22" s="208">
+        <f>T37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" ht="18">
+      <c r="A23" s="17">
+        <v>23</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="215"/>
+      <c r="D23" s="215"/>
+      <c r="E23" s="215"/>
+      <c r="F23" s="215"/>
+      <c r="G23" s="215"/>
+      <c r="H23" s="215"/>
+      <c r="I23" s="215"/>
+      <c r="J23" s="215"/>
+      <c r="K23" s="215"/>
+      <c r="L23" s="215"/>
+      <c r="M23" s="215"/>
+      <c r="N23" s="215"/>
+      <c r="O23" s="215"/>
+      <c r="P23" s="215"/>
+      <c r="Q23" s="215"/>
+      <c r="R23" s="215"/>
+      <c r="S23" s="215"/>
+      <c r="T23" s="215"/>
+      <c r="U23" s="215"/>
+      <c r="V23" s="215"/>
+      <c r="W23" s="215"/>
+      <c r="X23" s="215"/>
+      <c r="Y23" s="215"/>
+      <c r="Z23" s="215"/>
+      <c r="AA23" s="216"/>
+      <c r="AB23" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="21"/>
+      <c r="AD23" s="192"/>
+      <c r="AH23" s="209"/>
+      <c r="AI23" s="209"/>
+      <c r="AJ23" s="209"/>
+      <c r="AK23" s="209"/>
+      <c r="AL23" s="210"/>
+    </row>
+    <row r="24" spans="1:38" ht="15.75">
+      <c r="A24" s="11">
+        <v>24</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="213"/>
+      <c r="D24" s="213"/>
+      <c r="E24" s="213"/>
+      <c r="F24" s="213"/>
+      <c r="G24" s="213"/>
+      <c r="H24" s="213"/>
+      <c r="I24" s="213"/>
+      <c r="J24" s="213"/>
+      <c r="K24" s="213"/>
+      <c r="L24" s="213"/>
+      <c r="M24" s="213"/>
+      <c r="N24" s="213"/>
+      <c r="O24" s="213"/>
+      <c r="P24" s="213"/>
+      <c r="Q24" s="213"/>
+      <c r="R24" s="213"/>
+      <c r="S24" s="213"/>
+      <c r="T24" s="213"/>
+      <c r="U24" s="213"/>
+      <c r="V24" s="213"/>
+      <c r="W24" s="213"/>
+      <c r="X24" s="213"/>
+      <c r="Y24" s="213"/>
+      <c r="Z24" s="213"/>
+      <c r="AA24" s="214"/>
+      <c r="AB24" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="21"/>
+      <c r="AD24" s="192"/>
+    </row>
+    <row r="25" spans="1:38" ht="15.75">
+      <c r="A25" s="17">
+        <v>25</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="215"/>
+      <c r="D25" s="215"/>
+      <c r="E25" s="215"/>
+      <c r="F25" s="215"/>
+      <c r="G25" s="215"/>
+      <c r="H25" s="215"/>
+      <c r="I25" s="215"/>
+      <c r="J25" s="215"/>
+      <c r="K25" s="215"/>
+      <c r="L25" s="215"/>
+      <c r="M25" s="215"/>
+      <c r="N25" s="215"/>
+      <c r="O25" s="215"/>
+      <c r="P25" s="215"/>
+      <c r="Q25" s="215"/>
+      <c r="R25" s="215"/>
+      <c r="S25" s="215"/>
+      <c r="T25" s="215"/>
+      <c r="U25" s="215"/>
+      <c r="V25" s="215"/>
+      <c r="W25" s="215"/>
+      <c r="X25" s="215"/>
+      <c r="Y25" s="215"/>
+      <c r="Z25" s="215"/>
+      <c r="AA25" s="216"/>
+      <c r="AB25" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="21"/>
+      <c r="AD25" s="192"/>
+    </row>
+    <row r="26" spans="1:38" ht="15.75">
+      <c r="A26" s="11">
+        <v>26</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="213"/>
+      <c r="D26" s="213"/>
+      <c r="E26" s="213"/>
+      <c r="F26" s="213"/>
+      <c r="G26" s="213"/>
+      <c r="H26" s="213"/>
+      <c r="I26" s="213"/>
+      <c r="J26" s="213"/>
+      <c r="K26" s="213"/>
+      <c r="L26" s="213"/>
+      <c r="M26" s="213"/>
+      <c r="N26" s="213"/>
+      <c r="O26" s="213"/>
+      <c r="P26" s="213"/>
+      <c r="Q26" s="213"/>
+      <c r="R26" s="213"/>
+      <c r="S26" s="213"/>
+      <c r="T26" s="213"/>
+      <c r="U26" s="213"/>
+      <c r="V26" s="213"/>
+      <c r="W26" s="213"/>
+      <c r="X26" s="213"/>
+      <c r="Y26" s="213"/>
+      <c r="Z26" s="213"/>
+      <c r="AA26" s="214"/>
+      <c r="AB26" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC26" s="16"/>
+      <c r="AD26" s="192"/>
+    </row>
+    <row r="27" spans="1:38" ht="15.75">
+      <c r="A27" s="17">
+        <v>27</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="215"/>
+      <c r="D27" s="215"/>
+      <c r="E27" s="215"/>
+      <c r="F27" s="215"/>
+      <c r="G27" s="215"/>
+      <c r="H27" s="215"/>
+      <c r="I27" s="215"/>
+      <c r="J27" s="215"/>
+      <c r="K27" s="215"/>
+      <c r="L27" s="215"/>
+      <c r="M27" s="215"/>
+      <c r="N27" s="215"/>
+      <c r="O27" s="215"/>
+      <c r="P27" s="215"/>
+      <c r="Q27" s="215"/>
+      <c r="R27" s="215"/>
+      <c r="S27" s="215"/>
+      <c r="T27" s="215"/>
+      <c r="U27" s="215"/>
+      <c r="V27" s="215"/>
+      <c r="W27" s="215"/>
+      <c r="X27" s="215"/>
+      <c r="Y27" s="215"/>
+      <c r="Z27" s="215"/>
+      <c r="AA27" s="216"/>
+      <c r="AB27" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC27" s="21"/>
+      <c r="AD27" s="192"/>
+    </row>
+    <row r="28" spans="1:38" ht="15.75">
+      <c r="A28" s="11">
+        <v>28</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="213"/>
+      <c r="D28" s="213"/>
+      <c r="E28" s="213"/>
+      <c r="F28" s="213"/>
+      <c r="G28" s="213"/>
+      <c r="H28" s="213"/>
+      <c r="I28" s="213"/>
+      <c r="J28" s="213"/>
+      <c r="K28" s="213"/>
+      <c r="L28" s="213"/>
+      <c r="M28" s="213"/>
+      <c r="N28" s="213"/>
+      <c r="O28" s="213"/>
+      <c r="P28" s="213"/>
+      <c r="Q28" s="213"/>
+      <c r="R28" s="213"/>
+      <c r="S28" s="213"/>
+      <c r="T28" s="213"/>
+      <c r="U28" s="213"/>
+      <c r="V28" s="213"/>
+      <c r="W28" s="213"/>
+      <c r="X28" s="213"/>
+      <c r="Y28" s="213"/>
+      <c r="Z28" s="213"/>
+      <c r="AA28" s="214"/>
+      <c r="AB28" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC28" s="21"/>
+      <c r="AD28" s="192"/>
+    </row>
+    <row r="29" spans="1:38" ht="15.75">
+      <c r="A29" s="17">
+        <v>29</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="215"/>
+      <c r="D29" s="215"/>
+      <c r="E29" s="215"/>
+      <c r="F29" s="215"/>
+      <c r="G29" s="215"/>
+      <c r="H29" s="215"/>
+      <c r="I29" s="215"/>
+      <c r="J29" s="215"/>
+      <c r="K29" s="215"/>
+      <c r="L29" s="215"/>
+      <c r="M29" s="215"/>
+      <c r="N29" s="215"/>
+      <c r="O29" s="215"/>
+      <c r="P29" s="215"/>
+      <c r="Q29" s="215"/>
+      <c r="R29" s="215"/>
+      <c r="S29" s="215"/>
+      <c r="T29" s="215"/>
+      <c r="U29" s="215"/>
+      <c r="V29" s="215"/>
+      <c r="W29" s="215"/>
+      <c r="X29" s="215"/>
+      <c r="Y29" s="215"/>
+      <c r="Z29" s="215"/>
+      <c r="AA29" s="216"/>
+      <c r="AB29" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC29" s="21"/>
+      <c r="AD29" s="192"/>
+    </row>
+    <row r="30" spans="1:38" ht="15.75">
+      <c r="A30" s="11">
+        <v>30</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="213"/>
+      <c r="F30" s="213"/>
+      <c r="G30" s="213"/>
+      <c r="H30" s="213"/>
+      <c r="I30" s="213"/>
+      <c r="J30" s="213"/>
+      <c r="K30" s="213"/>
+      <c r="L30" s="213"/>
+      <c r="M30" s="213"/>
+      <c r="N30" s="213"/>
+      <c r="O30" s="213"/>
+      <c r="P30" s="213"/>
+      <c r="Q30" s="213"/>
+      <c r="R30" s="213"/>
+      <c r="S30" s="213"/>
+      <c r="T30" s="213"/>
+      <c r="U30" s="213"/>
+      <c r="V30" s="213"/>
+      <c r="W30" s="213"/>
+      <c r="X30" s="213"/>
+      <c r="Y30" s="213"/>
+      <c r="Z30" s="213"/>
+      <c r="AA30" s="214"/>
+      <c r="AB30" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC30" s="21"/>
+      <c r="AD30" s="192"/>
+    </row>
+    <row r="31" spans="1:38" ht="15.75">
+      <c r="A31" s="17">
+        <v>31</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="215"/>
+      <c r="D31" s="215"/>
+      <c r="E31" s="215"/>
+      <c r="F31" s="215"/>
+      <c r="G31" s="215"/>
+      <c r="H31" s="215"/>
+      <c r="I31" s="215"/>
+      <c r="J31" s="215"/>
+      <c r="K31" s="215"/>
+      <c r="L31" s="215"/>
+      <c r="M31" s="215"/>
+      <c r="N31" s="215"/>
+      <c r="O31" s="215"/>
+      <c r="P31" s="215"/>
+      <c r="Q31" s="215"/>
+      <c r="R31" s="215"/>
+      <c r="S31" s="215"/>
+      <c r="T31" s="215"/>
+      <c r="U31" s="215"/>
+      <c r="V31" s="215"/>
+      <c r="W31" s="215"/>
+      <c r="X31" s="215"/>
+      <c r="Y31" s="215"/>
+      <c r="Z31" s="215"/>
+      <c r="AA31" s="216"/>
+      <c r="AB31" s="15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC31" s="21"/>
+      <c r="AD31" s="192"/>
+    </row>
+    <row r="32" spans="1:38" ht="15.75">
+      <c r="A32" s="11">
+        <v>1</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="217"/>
+      <c r="D32" s="217"/>
+      <c r="E32" s="217"/>
+      <c r="F32" s="217"/>
+      <c r="G32" s="217"/>
+      <c r="H32" s="217"/>
+      <c r="I32" s="217"/>
+      <c r="J32" s="217"/>
+      <c r="K32" s="217"/>
+      <c r="L32" s="217"/>
+      <c r="M32" s="217"/>
+      <c r="N32" s="217"/>
+      <c r="O32" s="217"/>
+      <c r="P32" s="217"/>
+      <c r="Q32" s="217"/>
+      <c r="R32" s="217"/>
+      <c r="S32" s="217"/>
+      <c r="T32" s="217"/>
+      <c r="U32" s="217"/>
+      <c r="V32" s="217"/>
+      <c r="W32" s="217"/>
+      <c r="X32" s="217"/>
+      <c r="Y32" s="217"/>
+      <c r="Z32" s="217"/>
+      <c r="AA32" s="218"/>
+      <c r="AB32" s="15">
+        <f>SUM(C32:AA32)</f>
+        <v>0</v>
+      </c>
+      <c r="AC32" s="21"/>
+      <c r="AD32" s="192"/>
+    </row>
+    <row r="33" spans="1:34" ht="15.75">
+      <c r="A33" s="17">
+        <v>2</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="219"/>
+      <c r="D33" s="219"/>
+      <c r="E33" s="219"/>
+      <c r="F33" s="219"/>
+      <c r="G33" s="219"/>
+      <c r="H33" s="219"/>
+      <c r="I33" s="219"/>
+      <c r="J33" s="219"/>
+      <c r="K33" s="219"/>
+      <c r="L33" s="219"/>
+      <c r="M33" s="219"/>
+      <c r="N33" s="219"/>
+      <c r="O33" s="219"/>
+      <c r="P33" s="219"/>
+      <c r="Q33" s="219"/>
+      <c r="R33" s="219"/>
+      <c r="S33" s="219"/>
+      <c r="T33" s="219"/>
+      <c r="U33" s="219"/>
+      <c r="V33" s="219"/>
+      <c r="W33" s="219"/>
+      <c r="X33" s="219"/>
+      <c r="Y33" s="219"/>
+      <c r="Z33" s="219"/>
+      <c r="AA33" s="219"/>
+      <c r="AB33" s="211">
+        <f t="shared" ref="AB33:AB35" si="6">SUM(C33:AA33)</f>
+        <v>0</v>
+      </c>
+      <c r="AC33" s="21"/>
+      <c r="AD33" s="192"/>
+    </row>
+    <row r="34" spans="1:34" ht="15.75">
+      <c r="A34" s="11">
+        <v>3</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="220"/>
+      <c r="D34" s="220"/>
+      <c r="E34" s="220"/>
+      <c r="F34" s="220"/>
+      <c r="G34" s="220"/>
+      <c r="H34" s="220"/>
+      <c r="I34" s="220"/>
+      <c r="J34" s="220"/>
+      <c r="K34" s="220"/>
+      <c r="L34" s="220"/>
+      <c r="M34" s="220"/>
+      <c r="N34" s="220"/>
+      <c r="O34" s="220"/>
+      <c r="P34" s="220"/>
+      <c r="Q34" s="220"/>
+      <c r="R34" s="220"/>
+      <c r="S34" s="220"/>
+      <c r="T34" s="220"/>
+      <c r="U34" s="220"/>
+      <c r="V34" s="220"/>
+      <c r="W34" s="220"/>
+      <c r="X34" s="220"/>
+      <c r="Y34" s="220"/>
+      <c r="Z34" s="220"/>
+      <c r="AA34" s="220"/>
+      <c r="AB34" s="211">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC34" s="21"/>
+      <c r="AD34" s="192"/>
+    </row>
+    <row r="35" spans="1:34" ht="15.75">
+      <c r="A35" s="17">
+        <v>4</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="219"/>
+      <c r="D35" s="219"/>
+      <c r="E35" s="219"/>
+      <c r="F35" s="219"/>
+      <c r="G35" s="219"/>
+      <c r="H35" s="219"/>
+      <c r="I35" s="219"/>
+      <c r="J35" s="219"/>
+      <c r="K35" s="219"/>
+      <c r="L35" s="219"/>
+      <c r="M35" s="219"/>
+      <c r="N35" s="219"/>
+      <c r="O35" s="219"/>
+      <c r="P35" s="219"/>
+      <c r="Q35" s="219"/>
+      <c r="R35" s="219"/>
+      <c r="S35" s="219"/>
+      <c r="T35" s="219"/>
+      <c r="U35" s="219"/>
+      <c r="V35" s="219"/>
+      <c r="W35" s="219"/>
+      <c r="X35" s="219"/>
+      <c r="Y35" s="219"/>
+      <c r="Z35" s="219"/>
+      <c r="AA35" s="219"/>
+      <c r="AB35" s="211">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC35" s="21"/>
+      <c r="AD35" s="192"/>
+    </row>
+    <row r="36" spans="1:34" ht="24" customHeight="1">
+      <c r="A36" s="204" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="204"/>
+      <c r="C36" s="146">
+        <f>SUM(C20:C35)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="146">
+        <f>SUM(D20:D35)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="146">
+        <f>SUM(E20:E35)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="146">
+        <f>SUM(F20:F35)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="146">
+        <f>SUM(G20:G35)</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="146">
+        <f>SUM(H20:H35)</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="146">
+        <f>SUM(I20:I35)</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="146">
+        <f>SUM(J20:J35)</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="146">
+        <f>SUM(K20:K35)</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="147">
+        <f>SUM(L20:L35)</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="147">
+        <f>SUM(M20:M35)</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="147">
+        <f>SUM(N20:N35)</f>
+        <v>0</v>
+      </c>
+      <c r="O36" s="147">
+        <f>SUM(O20:O35)</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="147">
+        <f>SUM(P20:P35)</f>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="147">
+        <f>SUM(Q20:Q35)</f>
+        <v>0</v>
+      </c>
+      <c r="R36" s="148">
+        <f>SUM(R20:R35)</f>
+        <v>0</v>
+      </c>
+      <c r="S36" s="148">
+        <f>SUM(S20:S35)</f>
+        <v>0</v>
+      </c>
+      <c r="T36" s="148">
+        <f>SUM(T20:T35)</f>
+        <v>0</v>
+      </c>
+      <c r="U36" s="148">
+        <f>SUM(U20:U35)</f>
+        <v>0</v>
+      </c>
+      <c r="V36" s="148">
+        <f>SUM(V20:V35)</f>
+        <v>0</v>
+      </c>
+      <c r="W36" s="148">
+        <f>SUM(W20:W35)</f>
+        <v>0</v>
+      </c>
+      <c r="X36" s="148">
+        <f>SUM(X20:X35)</f>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="148">
+        <f>SUM(Y20:Y35)</f>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="148">
+        <f>SUM(Z20:Z35)</f>
+        <v>0</v>
+      </c>
+      <c r="AA36" s="149">
+        <f>SUM(AA20:AA35)</f>
+        <v>0</v>
+      </c>
+      <c r="AB36" s="26">
+        <f>SUM(AB20:AB35)</f>
+        <v>0</v>
+      </c>
+      <c r="AC36" s="27">
+        <f>SUM(AC20:AC35)</f>
+        <v>0</v>
+      </c>
+      <c r="AD36" s="28">
+        <f>AC36-AB36</f>
+        <v>0</v>
+      </c>
+      <c r="AH36" s="165"/>
+    </row>
+    <row r="37" spans="1:34" ht="31.5" customHeight="1">
+      <c r="A37" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="191"/>
+      <c r="C37" s="31">
+        <f>SUM(C19,C36)</f>
+        <v>1451.82</v>
+      </c>
+      <c r="D37" s="31">
+        <f>SUM(D19,D36)</f>
+        <v>556.94000000000005</v>
+      </c>
+      <c r="E37" s="31">
+        <f>SUM(E19,E36)</f>
+        <v>300.95999999999998</v>
+      </c>
+      <c r="F37" s="31">
+        <f>SUM(F19,F36)</f>
+        <v>4586.51</v>
+      </c>
+      <c r="G37" s="31">
+        <f>SUM(G19,G36)</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="31">
+        <f>SUM(H19,H36)</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="31">
+        <f>SUM(I19,I36)</f>
+        <v>23855.8</v>
+      </c>
+      <c r="J37" s="31">
+        <f>SUM(J19,J36)</f>
+        <v>290</v>
+      </c>
+      <c r="K37" s="31">
+        <f>SUM(K19,K36)</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="31">
+        <f>SUM(L19,L36)</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="31">
+        <f>SUM(M19,M36)</f>
+        <v>2070</v>
+      </c>
+      <c r="N37" s="31">
+        <f>SUM(N19,N36)</f>
+        <v>0</v>
+      </c>
+      <c r="O37" s="31">
+        <f>SUM(O19,O36)</f>
+        <v>5400</v>
+      </c>
+      <c r="P37" s="31">
+        <f>SUM(P19,P36)</f>
+        <v>11093</v>
+      </c>
+      <c r="Q37" s="31">
+        <f>SUM(Q19,Q36)</f>
+        <v>300</v>
+      </c>
+      <c r="R37" s="31">
+        <f>SUM(R19,R36)</f>
+        <v>0</v>
+      </c>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31">
+        <f>SUM(T19,T36)</f>
+        <v>0</v>
+      </c>
+      <c r="U37" s="31">
+        <f>SUM(U19,U36)</f>
+        <v>1333</v>
+      </c>
+      <c r="V37" s="31">
+        <f>SUM(V19,V36)</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="31">
+        <f>SUM(W19,W36)</f>
+        <v>20890</v>
+      </c>
+      <c r="X37" s="31">
+        <f>SUM(X19,X36)</f>
+        <v>24307</v>
+      </c>
+      <c r="Y37" s="31">
+        <f>SUM(Y19,Y36)</f>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="31">
+        <f>SUM(Z19,Z36)</f>
+        <v>1000</v>
+      </c>
+      <c r="AA37" s="32">
+        <f>SUM(AA19,AA36)</f>
+        <v>0</v>
+      </c>
+      <c r="AB37" s="33">
+        <f>SUM(AB19,AB36)</f>
+        <v>97634.03</v>
+      </c>
+      <c r="AC37" s="34">
+        <f>SUM(AC19,AC36)</f>
+        <v>144200.85999999999</v>
+      </c>
+      <c r="AD37" s="169">
+        <f>SUM(AD19,AD36)</f>
+        <v>46566.829999999987</v>
+      </c>
+    </row>
+    <row r="41" spans="1:34">
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="36"/>
+      <c r="P41" s="36"/>
+      <c r="Q41" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="AD4:AD18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="AH19:AK19"/>
+    <mergeCell ref="AD20:AD35"/>
+    <mergeCell ref="AH20:AK20"/>
+    <mergeCell ref="AH21:AK21"/>
+    <mergeCell ref="AH22:AK22"/>
+    <mergeCell ref="AH23:AK23"/>
+    <mergeCell ref="AH11:AL13"/>
+    <mergeCell ref="AH14:AK14"/>
+    <mergeCell ref="AH15:AK15"/>
+    <mergeCell ref="AH16:AK16"/>
+    <mergeCell ref="AH17:AK17"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9902,32 +12484,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="171" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
+      <c r="Q1" s="171"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="171"/>
+      <c r="T1" s="171"/>
+      <c r="U1" s="171"/>
+      <c r="V1" s="171"/>
+      <c r="W1" s="171"/>
+      <c r="X1" s="171"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="107" t="s">
@@ -11126,10 +13708,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="140" t="s">
+      <c r="A31" s="172" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="140"/>
+      <c r="B31" s="172"/>
       <c r="C31" s="127">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -11252,32 +13834,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="173" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="173"/>
+      <c r="O1" s="173"/>
+      <c r="P1" s="173"/>
+      <c r="Q1" s="173"/>
+      <c r="R1" s="173"/>
+      <c r="S1" s="173"/>
+      <c r="T1" s="173"/>
+      <c r="U1" s="173"/>
+      <c r="V1" s="173"/>
+      <c r="W1" s="173"/>
+      <c r="X1" s="173"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="84" t="s">
@@ -12488,10 +15070,10 @@
       <c r="X31" s="101"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="142" t="s">
+      <c r="A32" s="174" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="142"/>
+      <c r="B32" s="174"/>
       <c r="C32" s="100">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -12614,33 +15196,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="173" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="141"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="173"/>
+      <c r="O1" s="173"/>
+      <c r="P1" s="173"/>
+      <c r="Q1" s="173"/>
+      <c r="R1" s="173"/>
+      <c r="S1" s="173"/>
+      <c r="T1" s="173"/>
+      <c r="U1" s="173"/>
+      <c r="V1" s="173"/>
+      <c r="W1" s="173"/>
+      <c r="X1" s="173"/>
+      <c r="Y1" s="173"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="84" t="s">
@@ -13458,10 +16040,10 @@
       <c r="Y19" s="92"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="143" t="s">
+      <c r="A20" s="175" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="144"/>
+      <c r="B20" s="176"/>
       <c r="C20" s="93">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -14181,10 +16763,10 @@
       <c r="Y35" s="92"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="143" t="s">
+      <c r="A36" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="144"/>
+      <c r="B36" s="176"/>
       <c r="C36" s="93">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -14279,10 +16861,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="145" t="s">
+      <c r="A37" s="177" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="145"/>
+      <c r="B37" s="177"/>
       <c r="C37" s="97">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -14412,33 +16994,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="178" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
-      <c r="T1" s="146"/>
-      <c r="U1" s="146"/>
-      <c r="V1" s="146"/>
-      <c r="W1" s="146"/>
-      <c r="X1" s="146"/>
-      <c r="Y1" s="146"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
+      <c r="M1" s="178"/>
+      <c r="N1" s="178"/>
+      <c r="O1" s="178"/>
+      <c r="P1" s="178"/>
+      <c r="Q1" s="178"/>
+      <c r="R1" s="178"/>
+      <c r="S1" s="178"/>
+      <c r="T1" s="178"/>
+      <c r="U1" s="178"/>
+      <c r="V1" s="178"/>
+      <c r="W1" s="178"/>
+      <c r="X1" s="178"/>
+      <c r="Y1" s="178"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="81" t="s">
@@ -15148,10 +17730,10 @@
       <c r="Y17" s="74"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="147" t="s">
+      <c r="A18" s="179" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="147"/>
+      <c r="B18" s="179"/>
       <c r="C18" s="82">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -15904,10 +18486,10 @@
       <c r="Y34" s="76"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="147" t="s">
+      <c r="A35" s="179" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="147"/>
+      <c r="B35" s="179"/>
       <c r="C35" s="82">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -16002,10 +18584,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="148" t="s">
+      <c r="A36" s="180" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="148"/>
+      <c r="B36" s="180"/>
       <c r="C36" s="72">
         <f>SUM(C18,C35)</f>
         <v>19167.810000000001</v>
@@ -16119,10 +18701,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16143,33 +18725,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="181" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="149"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="149"/>
-      <c r="W1" s="149"/>
-      <c r="X1" s="149"/>
-      <c r="Y1" s="149"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="181"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="181"/>
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="181"/>
+      <c r="T1" s="181"/>
+      <c r="U1" s="181"/>
+      <c r="V1" s="181"/>
+      <c r="W1" s="181"/>
+      <c r="X1" s="181"/>
+      <c r="Y1" s="181"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -16908,10 +19490,10 @@
       <c r="Y17" s="74"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="150" t="s">
+      <c r="A18" s="182" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="150"/>
+      <c r="B18" s="182"/>
       <c r="C18" s="60">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -17559,10 +20141,10 @@
       <c r="Y34" s="76"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="150" t="s">
+      <c r="A35" s="182" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="150"/>
+      <c r="B35" s="182"/>
       <c r="C35" s="60">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -17657,10 +20239,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="151" t="s">
+      <c r="A36" s="183" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="151"/>
+      <c r="B36" s="183"/>
       <c r="C36" s="80">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -17774,10 +20356,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17800,34 +20382,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="188" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
-      <c r="V1" s="152"/>
-      <c r="W1" s="152"/>
-      <c r="X1" s="152"/>
-      <c r="Y1" s="152"/>
-      <c r="Z1" s="152"/>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="188"/>
+      <c r="F1" s="188"/>
+      <c r="G1" s="188"/>
+      <c r="H1" s="188"/>
+      <c r="I1" s="188"/>
+      <c r="J1" s="188"/>
+      <c r="K1" s="188"/>
+      <c r="L1" s="188"/>
+      <c r="M1" s="188"/>
+      <c r="N1" s="188"/>
+      <c r="O1" s="188"/>
+      <c r="P1" s="188"/>
+      <c r="Q1" s="188"/>
+      <c r="R1" s="188"/>
+      <c r="S1" s="188"/>
+      <c r="T1" s="188"/>
+      <c r="U1" s="188"/>
+      <c r="V1" s="188"/>
+      <c r="W1" s="188"/>
+      <c r="X1" s="188"/>
+      <c r="Y1" s="188"/>
+      <c r="Z1" s="188"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -17980,7 +20562,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.67000000001</v>
       </c>
-      <c r="Z3" s="155"/>
+      <c r="Z3" s="186"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="52">
@@ -18030,7 +20612,7 @@
       </c>
       <c r="X4" s="50"/>
       <c r="Y4" s="56"/>
-      <c r="Z4" s="155"/>
+      <c r="Z4" s="186"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="45">
@@ -18070,7 +20652,7 @@
       </c>
       <c r="X5" s="50"/>
       <c r="Y5" s="56"/>
-      <c r="Z5" s="155"/>
+      <c r="Z5" s="186"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="52">
@@ -18111,7 +20693,7 @@
       </c>
       <c r="X6" s="50"/>
       <c r="Y6" s="56"/>
-      <c r="Z6" s="155"/>
+      <c r="Z6" s="186"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="45">
@@ -18155,7 +20737,7 @@
       </c>
       <c r="X7" s="50"/>
       <c r="Y7" s="56"/>
-      <c r="Z7" s="155"/>
+      <c r="Z7" s="186"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="52">
@@ -18197,14 +20779,14 @@
       </c>
       <c r="X8" s="50"/>
       <c r="Y8" s="56"/>
-      <c r="Z8" s="155"/>
-      <c r="AC8" s="156" t="s">
+      <c r="Z8" s="186"/>
+      <c r="AC8" s="187" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="156"/>
-      <c r="AE8" s="156"/>
-      <c r="AF8" s="156"/>
-      <c r="AG8" s="156"/>
+      <c r="AD8" s="187"/>
+      <c r="AE8" s="187"/>
+      <c r="AF8" s="187"/>
+      <c r="AG8" s="187"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="45">
@@ -18243,12 +20825,12 @@
       </c>
       <c r="X9" s="50"/>
       <c r="Y9" s="56"/>
-      <c r="Z9" s="155"/>
-      <c r="AC9" s="156"/>
-      <c r="AD9" s="156"/>
-      <c r="AE9" s="156"/>
-      <c r="AF9" s="156"/>
-      <c r="AG9" s="156"/>
+      <c r="Z9" s="186"/>
+      <c r="AC9" s="187"/>
+      <c r="AD9" s="187"/>
+      <c r="AE9" s="187"/>
+      <c r="AF9" s="187"/>
+      <c r="AG9" s="187"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="52">
@@ -18292,12 +20874,12 @@
       </c>
       <c r="X10" s="50"/>
       <c r="Y10" s="56"/>
-      <c r="Z10" s="155"/>
-      <c r="AC10" s="156"/>
-      <c r="AD10" s="156"/>
-      <c r="AE10" s="156"/>
-      <c r="AF10" s="156"/>
-      <c r="AG10" s="156"/>
+      <c r="Z10" s="186"/>
+      <c r="AC10" s="187"/>
+      <c r="AD10" s="187"/>
+      <c r="AE10" s="187"/>
+      <c r="AF10" s="187"/>
+      <c r="AG10" s="187"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="45">
@@ -18337,13 +20919,13 @@
       </c>
       <c r="X11" s="50"/>
       <c r="Y11" s="56"/>
-      <c r="Z11" s="155"/>
-      <c r="AC11" s="153" t="s">
+      <c r="Z11" s="186"/>
+      <c r="AC11" s="184" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="153"/>
-      <c r="AE11" s="153"/>
-      <c r="AF11" s="153"/>
+      <c r="AD11" s="184"/>
+      <c r="AE11" s="184"/>
+      <c r="AF11" s="184"/>
       <c r="AG11" s="57">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -18384,13 +20966,13 @@
       </c>
       <c r="X12" s="50"/>
       <c r="Y12" s="56"/>
-      <c r="Z12" s="155"/>
-      <c r="AC12" s="153" t="s">
+      <c r="Z12" s="186"/>
+      <c r="AC12" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="AD12" s="153"/>
-      <c r="AE12" s="153"/>
-      <c r="AF12" s="153"/>
+      <c r="AD12" s="184"/>
+      <c r="AE12" s="184"/>
+      <c r="AF12" s="184"/>
       <c r="AG12" s="57">
         <f>Y27</f>
         <v>20000</v>
@@ -18435,13 +21017,13 @@
       </c>
       <c r="X13" s="50"/>
       <c r="Y13" s="56"/>
-      <c r="Z13" s="155"/>
-      <c r="AC13" s="153" t="s">
+      <c r="Z13" s="186"/>
+      <c r="AC13" s="184" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="153"/>
-      <c r="AE13" s="153"/>
-      <c r="AF13" s="153"/>
+      <c r="AD13" s="184"/>
+      <c r="AE13" s="184"/>
+      <c r="AF13" s="184"/>
       <c r="AG13" s="57">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -18487,13 +21069,13 @@
       <c r="Y14" s="51">
         <v>37634</v>
       </c>
-      <c r="Z14" s="155"/>
-      <c r="AC14" s="153" t="s">
+      <c r="Z14" s="186"/>
+      <c r="AC14" s="184" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="153"/>
-      <c r="AE14" s="153"/>
-      <c r="AF14" s="153"/>
+      <c r="AD14" s="184"/>
+      <c r="AE14" s="184"/>
+      <c r="AF14" s="184"/>
       <c r="AG14" s="57">
         <f>W38</f>
         <v>177971.36</v>
@@ -18543,13 +21125,13 @@
       </c>
       <c r="X15" s="50"/>
       <c r="Y15" s="56"/>
-      <c r="Z15" s="155"/>
-      <c r="AC15" s="153" t="s">
+      <c r="Z15" s="186"/>
+      <c r="AC15" s="184" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="153"/>
-      <c r="AE15" s="153"/>
-      <c r="AF15" s="153"/>
+      <c r="AD15" s="184"/>
+      <c r="AE15" s="184"/>
+      <c r="AF15" s="184"/>
       <c r="AG15" s="57">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -18598,7 +21180,17 @@
       </c>
       <c r="X16" s="50"/>
       <c r="Y16" s="56"/>
-      <c r="Z16" s="155"/>
+      <c r="Z16" s="186"/>
+      <c r="AC16" s="184" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD16" s="184"/>
+      <c r="AE16" s="184"/>
+      <c r="AF16" s="184"/>
+      <c r="AG16" s="57">
+        <f>Q38</f>
+        <v>27468.98</v>
+      </c>
     </row>
     <row r="17" spans="1:28" ht="15.75">
       <c r="A17" s="45">
@@ -18650,7 +21242,7 @@
       <c r="Y17" s="59">
         <v>15000</v>
       </c>
-      <c r="Z17" s="155"/>
+      <c r="Z17" s="186"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="52">
@@ -18691,7 +21283,7 @@
       </c>
       <c r="X18" s="50"/>
       <c r="Y18" s="56"/>
-      <c r="Z18" s="155"/>
+      <c r="Z18" s="186"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="45">
@@ -18735,13 +21327,13 @@
       <c r="Y19" s="59">
         <v>10000</v>
       </c>
-      <c r="Z19" s="155"/>
+      <c r="Z19" s="186"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="150" t="s">
+      <c r="A20" s="182" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="150"/>
+      <c r="B20" s="182"/>
       <c r="C20" s="60">
         <f t="shared" ref="C20:V20" si="1">SUM(C3:C17)</f>
         <v>10942.99</v>
@@ -18884,7 +21476,7 @@
       <c r="Y21" s="51">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="155"/>
+      <c r="Z21" s="186"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="52">
@@ -18930,7 +21522,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="56"/>
-      <c r="Z22" s="155"/>
+      <c r="Z22" s="186"/>
       <c r="AB22" s="29"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -18974,7 +21566,7 @@
       </c>
       <c r="X23" s="50"/>
       <c r="Y23" s="56"/>
-      <c r="Z23" s="155"/>
+      <c r="Z23" s="186"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="52">
@@ -19018,7 +21610,7 @@
       </c>
       <c r="X24" s="50"/>
       <c r="Y24" s="56"/>
-      <c r="Z24" s="155"/>
+      <c r="Z24" s="186"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="45">
@@ -19062,7 +21654,7 @@
       </c>
       <c r="X25" s="50"/>
       <c r="Y25" s="56"/>
-      <c r="Z25" s="155"/>
+      <c r="Z25" s="186"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="52">
@@ -19101,7 +21693,7 @@
       </c>
       <c r="X26" s="50"/>
       <c r="Y26" s="56"/>
-      <c r="Z26" s="155"/>
+      <c r="Z26" s="186"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="45">
@@ -19146,7 +21738,7 @@
       <c r="Y27" s="66">
         <v>20000</v>
       </c>
-      <c r="Z27" s="155"/>
+      <c r="Z27" s="186"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="52">
@@ -19188,7 +21780,7 @@
       </c>
       <c r="X28" s="50"/>
       <c r="Y28" s="56"/>
-      <c r="Z28" s="155"/>
+      <c r="Z28" s="186"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="45">
@@ -19227,7 +21819,7 @@
       </c>
       <c r="X29" s="50"/>
       <c r="Y29" s="56"/>
-      <c r="Z29" s="155"/>
+      <c r="Z29" s="186"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="52">
@@ -19267,7 +21859,7 @@
       </c>
       <c r="X30" s="50"/>
       <c r="Y30" s="56"/>
-      <c r="Z30" s="155"/>
+      <c r="Z30" s="186"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="45">
@@ -19302,7 +21894,7 @@
       </c>
       <c r="X31" s="50"/>
       <c r="Y31" s="56"/>
-      <c r="Z31" s="155"/>
+      <c r="Z31" s="186"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="52">
@@ -19337,7 +21929,7 @@
       </c>
       <c r="X32" s="50"/>
       <c r="Y32" s="56"/>
-      <c r="Z32" s="155"/>
+      <c r="Z32" s="186"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="45">
@@ -19374,7 +21966,7 @@
       <c r="Y33" s="67">
         <v>10000</v>
       </c>
-      <c r="Z33" s="155"/>
+      <c r="Z33" s="186"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="52">
@@ -19413,7 +22005,7 @@
       </c>
       <c r="X34" s="50"/>
       <c r="Y34" s="56"/>
-      <c r="Z34" s="155"/>
+      <c r="Z34" s="186"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="45">
@@ -19457,7 +22049,7 @@
       </c>
       <c r="X35" s="50"/>
       <c r="Y35" s="56"/>
-      <c r="Z35" s="155"/>
+      <c r="Z35" s="186"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="52">
@@ -19498,13 +22090,13 @@
       </c>
       <c r="X36" s="50"/>
       <c r="Y36" s="56"/>
-      <c r="Z36" s="155"/>
+      <c r="Z36" s="186"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="150" t="s">
+      <c r="A37" s="182" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="150"/>
+      <c r="B37" s="182"/>
       <c r="C37" s="60">
         <f>SUM(C21:C36)</f>
         <v>3393</v>
@@ -19603,10 +22195,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="154" t="s">
+      <c r="A38" s="185" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="154"/>
+      <c r="B38" s="185"/>
       <c r="C38" s="69">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -19717,7 +22309,12 @@
       <c r="K42" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A37:B37"/>
@@ -19725,11 +22322,7 @@
     <mergeCell ref="Z3:Z19"/>
     <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC8:AG10"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="AC16:AF16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -19750,78 +22343,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="194" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="157"/>
-      <c r="N1" s="157"/>
-      <c r="O1" s="157"/>
-      <c r="P1" s="157"/>
-      <c r="Q1" s="157"/>
-      <c r="R1" s="157"/>
-      <c r="S1" s="157"/>
-      <c r="T1" s="157"/>
-      <c r="U1" s="157"/>
-      <c r="V1" s="157"/>
-      <c r="W1" s="157"/>
-      <c r="X1" s="157"/>
-      <c r="Y1" s="157"/>
-      <c r="Z1" s="157"/>
-      <c r="AA1" s="157"/>
-      <c r="AB1" s="157"/>
-      <c r="AC1" s="157"/>
-      <c r="AD1" s="157"/>
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="194"/>
+      <c r="I1" s="194"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="194"/>
+      <c r="Y1" s="194"/>
+      <c r="Z1" s="194"/>
+      <c r="AA1" s="194"/>
+      <c r="AB1" s="194"/>
+      <c r="AC1" s="194"/>
+      <c r="AD1" s="194"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="158"/>
-      <c r="B2" s="159"/>
-      <c r="C2" s="160" t="s">
+      <c r="A2" s="195"/>
+      <c r="B2" s="196"/>
+      <c r="C2" s="197" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
-      <c r="L2" s="161" t="s">
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="161"/>
-      <c r="N2" s="161"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="161"/>
-      <c r="R2" s="162" t="s">
+      <c r="M2" s="198"/>
+      <c r="N2" s="198"/>
+      <c r="O2" s="198"/>
+      <c r="P2" s="198"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="199" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="162"/>
-      <c r="T2" s="162"/>
-      <c r="U2" s="162"/>
-      <c r="V2" s="162"/>
-      <c r="W2" s="162"/>
-      <c r="X2" s="162"/>
-      <c r="Y2" s="162"/>
-      <c r="Z2" s="162"/>
-      <c r="AA2" s="162"/>
-      <c r="AB2" s="163" t="s">
+      <c r="S2" s="199"/>
+      <c r="T2" s="199"/>
+      <c r="U2" s="199"/>
+      <c r="V2" s="199"/>
+      <c r="W2" s="199"/>
+      <c r="X2" s="199"/>
+      <c r="Y2" s="199"/>
+      <c r="Z2" s="199"/>
+      <c r="AA2" s="199"/>
+      <c r="AB2" s="200" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="163"/>
-      <c r="AD2" s="163"/>
+      <c r="AC2" s="200"/>
+      <c r="AD2" s="200"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -19988,7 +22581,7 @@
         <f>37635+40252.26+18817.85</f>
         <v>96705.11</v>
       </c>
-      <c r="AD4" s="167"/>
+      <c r="AD4" s="192"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -20038,7 +22631,7 @@
         <v>16503.13</v>
       </c>
       <c r="AC5" s="21"/>
-      <c r="AD5" s="167"/>
+      <c r="AD5" s="192"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -20081,7 +22674,7 @@
         <v>996.61</v>
       </c>
       <c r="AC6" s="21"/>
-      <c r="AD6" s="167"/>
+      <c r="AD6" s="192"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -20134,7 +22727,7 @@
         <v>5968</v>
       </c>
       <c r="AC7" s="21"/>
-      <c r="AD7" s="167"/>
+      <c r="AD7" s="192"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -20180,7 +22773,7 @@
         <v>12168.98</v>
       </c>
       <c r="AC8" s="21"/>
-      <c r="AD8" s="167"/>
+      <c r="AD8" s="192"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -20228,7 +22821,7 @@
         <v>5970</v>
       </c>
       <c r="AC9" s="21"/>
-      <c r="AD9" s="167"/>
+      <c r="AD9" s="192"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -20276,7 +22869,7 @@
         <v>3257</v>
       </c>
       <c r="AC10" s="21"/>
-      <c r="AD10" s="167"/>
+      <c r="AD10" s="192"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -20320,14 +22913,14 @@
         <v>1034</v>
       </c>
       <c r="AC11" s="21"/>
-      <c r="AD11" s="167"/>
-      <c r="AH11" s="168" t="s">
+      <c r="AD11" s="192"/>
+      <c r="AH11" s="193" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="168"/>
-      <c r="AJ11" s="168"/>
-      <c r="AK11" s="168"/>
-      <c r="AL11" s="168"/>
+      <c r="AI11" s="193"/>
+      <c r="AJ11" s="193"/>
+      <c r="AK11" s="193"/>
+      <c r="AL11" s="193"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -20374,12 +22967,12 @@
         <v>3586</v>
       </c>
       <c r="AC12" s="21"/>
-      <c r="AD12" s="167"/>
-      <c r="AH12" s="168"/>
-      <c r="AI12" s="168"/>
-      <c r="AJ12" s="168"/>
-      <c r="AK12" s="168"/>
-      <c r="AL12" s="168"/>
+      <c r="AD12" s="192"/>
+      <c r="AH12" s="193"/>
+      <c r="AI12" s="193"/>
+      <c r="AJ12" s="193"/>
+      <c r="AK12" s="193"/>
+      <c r="AL12" s="193"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -20426,12 +23019,12 @@
         <v>5889</v>
       </c>
       <c r="AC13" s="21"/>
-      <c r="AD13" s="167"/>
-      <c r="AH13" s="168"/>
-      <c r="AI13" s="168"/>
-      <c r="AJ13" s="168"/>
-      <c r="AK13" s="168"/>
-      <c r="AL13" s="168"/>
+      <c r="AD13" s="192"/>
+      <c r="AH13" s="193"/>
+      <c r="AI13" s="193"/>
+      <c r="AJ13" s="193"/>
+      <c r="AK13" s="193"/>
+      <c r="AL13" s="193"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -20477,13 +23070,13 @@
         <v>7092.93</v>
       </c>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="167"/>
-      <c r="AH14" s="164" t="s">
+      <c r="AD14" s="192"/>
+      <c r="AH14" s="189" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="164"/>
-      <c r="AJ14" s="164"/>
-      <c r="AK14" s="164"/>
+      <c r="AI14" s="189"/>
+      <c r="AJ14" s="189"/>
+      <c r="AK14" s="189"/>
       <c r="AL14" s="22">
         <f>AC4+AC20</f>
         <v>133443.15</v>
@@ -20541,13 +23134,13 @@
         <v>6644.28</v>
       </c>
       <c r="AC15" s="16"/>
-      <c r="AD15" s="167"/>
-      <c r="AH15" s="164" t="s">
+      <c r="AD15" s="192"/>
+      <c r="AH15" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="164"/>
-      <c r="AJ15" s="164"/>
-      <c r="AK15" s="164"/>
+      <c r="AI15" s="189"/>
+      <c r="AJ15" s="189"/>
+      <c r="AK15" s="189"/>
       <c r="AL15" s="22">
         <f>AC29</f>
         <v>1000</v>
@@ -20602,13 +23195,13 @@
         <v>5105.1899999999996</v>
       </c>
       <c r="AC16" s="21"/>
-      <c r="AD16" s="167"/>
-      <c r="AH16" s="164" t="s">
+      <c r="AD16" s="192"/>
+      <c r="AH16" s="189" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="164"/>
-      <c r="AJ16" s="164"/>
-      <c r="AK16" s="164"/>
+      <c r="AI16" s="189"/>
+      <c r="AJ16" s="189"/>
+      <c r="AK16" s="189"/>
       <c r="AL16" s="22">
         <f>AC21+AC34</f>
         <v>11000</v>
@@ -20653,13 +23246,13 @@
         <v>280.97000000000003</v>
       </c>
       <c r="AC17" s="21"/>
-      <c r="AD17" s="167"/>
-      <c r="AH17" s="164" t="s">
+      <c r="AD17" s="192"/>
+      <c r="AH17" s="189" t="s">
         <v>64</v>
       </c>
-      <c r="AI17" s="164"/>
-      <c r="AJ17" s="164"/>
-      <c r="AK17" s="164"/>
+      <c r="AI17" s="189"/>
+      <c r="AJ17" s="189"/>
+      <c r="AK17" s="189"/>
       <c r="AL17" s="22">
         <f>AB36</f>
         <v>146501.73000000001</v>
@@ -20708,23 +23301,23 @@
         <v>956.98</v>
       </c>
       <c r="AC18" s="21"/>
-      <c r="AD18" s="167"/>
-      <c r="AH18" s="164" t="s">
+      <c r="AD18" s="192"/>
+      <c r="AH18" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="AI18" s="164"/>
-      <c r="AJ18" s="164"/>
-      <c r="AK18" s="164"/>
+      <c r="AI18" s="189"/>
+      <c r="AJ18" s="189"/>
+      <c r="AK18" s="189"/>
       <c r="AL18" s="22">
         <f>SUM(C36:K36)</f>
         <v>56967.92</v>
       </c>
     </row>
     <row r="19" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A19" s="165" t="s">
+      <c r="A19" s="190" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="165"/>
+      <c r="B19" s="190"/>
       <c r="C19" s="23">
         <f>SUM(C4:C18)</f>
         <v>1403.89</v>
@@ -20837,12 +23430,12 @@
         <f>AC19-AB19</f>
         <v>4280.0900000000101</v>
       </c>
-      <c r="AH19" s="164" t="s">
+      <c r="AH19" s="189" t="s">
         <v>84</v>
       </c>
-      <c r="AI19" s="164"/>
-      <c r="AJ19" s="164"/>
-      <c r="AK19" s="164"/>
+      <c r="AI19" s="189"/>
+      <c r="AJ19" s="189"/>
+      <c r="AK19" s="189"/>
       <c r="AL19" s="22">
         <f>SUM(L36:Q36)</f>
         <v>31394.13</v>
@@ -20903,13 +23496,13 @@
       <c r="AC20" s="16">
         <v>36738.04</v>
       </c>
-      <c r="AD20" s="167"/>
-      <c r="AH20" s="164" t="s">
+      <c r="AD20" s="192"/>
+      <c r="AH20" s="189" t="s">
         <v>85</v>
       </c>
-      <c r="AI20" s="164"/>
-      <c r="AJ20" s="164"/>
-      <c r="AK20" s="164"/>
+      <c r="AI20" s="189"/>
+      <c r="AJ20" s="189"/>
+      <c r="AK20" s="189"/>
       <c r="AL20" s="22">
         <f>W36</f>
         <v>35678.97</v>
@@ -20964,14 +23557,14 @@
       <c r="AC21" s="37">
         <v>10000</v>
       </c>
-      <c r="AD21" s="167"/>
+      <c r="AD21" s="192"/>
       <c r="AF21" s="29"/>
-      <c r="AH21" s="164" t="s">
+      <c r="AH21" s="189" t="s">
         <v>86</v>
       </c>
-      <c r="AI21" s="164"/>
-      <c r="AJ21" s="164"/>
-      <c r="AK21" s="164"/>
+      <c r="AI21" s="189"/>
+      <c r="AJ21" s="189"/>
+      <c r="AK21" s="189"/>
       <c r="AL21" s="22">
         <f>SUM(U36:V36)</f>
         <v>11008.46</v>
@@ -21014,13 +23607,13 @@
         <v>0</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="167"/>
-      <c r="AH22" s="164" t="s">
+      <c r="AD22" s="192"/>
+      <c r="AH22" s="189" t="s">
         <v>32</v>
       </c>
-      <c r="AI22" s="164"/>
-      <c r="AJ22" s="164"/>
-      <c r="AK22" s="164"/>
+      <c r="AI22" s="189"/>
+      <c r="AJ22" s="189"/>
+      <c r="AK22" s="189"/>
       <c r="AL22" s="22">
         <f>T36</f>
         <v>0</v>
@@ -21075,13 +23668,13 @@
         <v>6881.28</v>
       </c>
       <c r="AC23" s="21"/>
-      <c r="AD23" s="167"/>
-      <c r="AH23" s="164" t="s">
+      <c r="AD23" s="192"/>
+      <c r="AH23" s="189" t="s">
         <v>87</v>
       </c>
-      <c r="AI23" s="164"/>
-      <c r="AJ23" s="164"/>
-      <c r="AK23" s="164"/>
+      <c r="AI23" s="189"/>
+      <c r="AJ23" s="189"/>
+      <c r="AK23" s="189"/>
       <c r="AL23" s="22">
         <f>X36</f>
         <v>5267.98</v>
@@ -21136,7 +23729,7 @@
         <v>6126.69</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="167"/>
+      <c r="AD24" s="192"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="17">
@@ -21180,7 +23773,7 @@
         <v>7750</v>
       </c>
       <c r="AC25" s="21"/>
-      <c r="AD25" s="167"/>
+      <c r="AD25" s="192"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="11">
@@ -21227,7 +23820,7 @@
         <v>2803</v>
       </c>
       <c r="AC26" s="16"/>
-      <c r="AD26" s="167"/>
+      <c r="AD26" s="192"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="17">
@@ -21275,7 +23868,7 @@
         <v>2088.96</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="167"/>
+      <c r="AD27" s="192"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="11">
@@ -21321,7 +23914,7 @@
         <v>3468</v>
       </c>
       <c r="AC28" s="21"/>
-      <c r="AD28" s="167"/>
+      <c r="AD28" s="192"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="17">
@@ -21374,7 +23967,7 @@
       <c r="AC29" s="21">
         <v>1000</v>
       </c>
-      <c r="AD29" s="167"/>
+      <c r="AD29" s="192"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="11">
@@ -21422,7 +24015,7 @@
         <v>4016.5</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="167"/>
+      <c r="AD30" s="192"/>
     </row>
     <row r="31" spans="1:38" ht="15.75">
       <c r="A31" s="17">
@@ -21466,7 +24059,7 @@
         <v>2801.78</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="167"/>
+      <c r="AD31" s="192"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
       <c r="A32" s="11">
@@ -21515,7 +24108,7 @@
         <v>3807.11</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="167"/>
+      <c r="AD32" s="192"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
       <c r="A33" s="17">
@@ -21559,7 +24152,7 @@
         <v>675.44</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="167"/>
+      <c r="AD33" s="192"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
       <c r="A34" s="11">
@@ -21603,13 +24196,13 @@
       <c r="AC34" s="37">
         <v>1000</v>
       </c>
-      <c r="AD34" s="167"/>
+      <c r="AD34" s="192"/>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A35" s="165" t="s">
+      <c r="A35" s="190" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="165"/>
+      <c r="B35" s="190"/>
       <c r="C35" s="23">
         <f t="shared" ref="C35:AC35" si="3">SUM(C20:C34)</f>
         <v>2169.6999999999998</v>
@@ -21724,10 +24317,10 @@
       </c>
     </row>
     <row r="36" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A36" s="166" t="s">
+      <c r="A36" s="191" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="166"/>
+      <c r="B36" s="191"/>
       <c r="C36" s="31">
         <f>SUM(C19,C35)</f>
         <v>3573.59</v>
@@ -21858,6 +24451,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AH23:AK23"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
@@ -21874,12 +24473,6 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="AH17:AK17"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -21900,78 +24493,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="194" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="157"/>
-      <c r="N1" s="157"/>
-      <c r="O1" s="157"/>
-      <c r="P1" s="157"/>
-      <c r="Q1" s="157"/>
-      <c r="R1" s="157"/>
-      <c r="S1" s="157"/>
-      <c r="T1" s="157"/>
-      <c r="U1" s="157"/>
-      <c r="V1" s="157"/>
-      <c r="W1" s="157"/>
-      <c r="X1" s="157"/>
-      <c r="Y1" s="157"/>
-      <c r="Z1" s="157"/>
-      <c r="AA1" s="157"/>
-      <c r="AB1" s="157"/>
-      <c r="AC1" s="157"/>
-      <c r="AD1" s="157"/>
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="194"/>
+      <c r="I1" s="194"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="194"/>
+      <c r="Y1" s="194"/>
+      <c r="Z1" s="194"/>
+      <c r="AA1" s="194"/>
+      <c r="AB1" s="194"/>
+      <c r="AC1" s="194"/>
+      <c r="AD1" s="194"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="158"/>
-      <c r="B2" s="159"/>
-      <c r="C2" s="160" t="s">
+      <c r="A2" s="195"/>
+      <c r="B2" s="196"/>
+      <c r="C2" s="197" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
-      <c r="L2" s="161" t="s">
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="161"/>
-      <c r="N2" s="161"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="161"/>
-      <c r="R2" s="162" t="s">
+      <c r="M2" s="198"/>
+      <c r="N2" s="198"/>
+      <c r="O2" s="198"/>
+      <c r="P2" s="198"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="199" t="s">
         <v>69</v>
       </c>
-      <c r="S2" s="162"/>
-      <c r="T2" s="162"/>
-      <c r="U2" s="162"/>
-      <c r="V2" s="162"/>
-      <c r="W2" s="162"/>
-      <c r="X2" s="162"/>
-      <c r="Y2" s="162"/>
-      <c r="Z2" s="162"/>
-      <c r="AA2" s="162"/>
-      <c r="AB2" s="163" t="s">
+      <c r="S2" s="199"/>
+      <c r="T2" s="199"/>
+      <c r="U2" s="199"/>
+      <c r="V2" s="199"/>
+      <c r="W2" s="199"/>
+      <c r="X2" s="199"/>
+      <c r="Y2" s="199"/>
+      <c r="Z2" s="199"/>
+      <c r="AA2" s="199"/>
+      <c r="AB2" s="200" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="163"/>
-      <c r="AD2" s="163"/>
+      <c r="AC2" s="200"/>
+      <c r="AD2" s="200"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -22061,7 +24654,7 @@
       <c r="AC3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AD3" s="201" t="s">
+      <c r="AD3" s="206" t="s">
         <v>5</v>
       </c>
       <c r="AE3" s="10"/>
@@ -22132,11 +24725,11 @@
         <f>SUM(C4:AA4)</f>
         <v>4117.99</v>
       </c>
-      <c r="AC4" s="198">
+      <c r="AC4" s="166">
         <f>66577.47+18817</f>
         <v>85394.47</v>
       </c>
-      <c r="AD4" s="167"/>
+      <c r="AD4" s="192"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="17">
@@ -22190,8 +24783,8 @@
         <f>SUM(C5:AA5)</f>
         <v>7116</v>
       </c>
-      <c r="AC5" s="200"/>
-      <c r="AD5" s="167"/>
+      <c r="AC5" s="168"/>
+      <c r="AD5" s="192"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="11">
@@ -22238,8 +24831,8 @@
         <f t="shared" ref="AB6:AB16" si="0">SUM(C6:AA6)</f>
         <v>17146</v>
       </c>
-      <c r="AC6" s="200"/>
-      <c r="AD6" s="167"/>
+      <c r="AC6" s="168"/>
+      <c r="AD6" s="192"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="17">
@@ -22295,8 +24888,8 @@
         <f t="shared" si="0"/>
         <v>6206.84</v>
       </c>
-      <c r="AC7" s="200"/>
-      <c r="AD7" s="167"/>
+      <c r="AC7" s="168"/>
+      <c r="AD7" s="192"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="11">
@@ -22354,8 +24947,8 @@
         <f t="shared" si="0"/>
         <v>8204</v>
       </c>
-      <c r="AC8" s="200"/>
-      <c r="AD8" s="167"/>
+      <c r="AC8" s="168"/>
+      <c r="AD8" s="192"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="17">
@@ -22403,8 +24996,8 @@
         <f t="shared" si="0"/>
         <v>8276</v>
       </c>
-      <c r="AC9" s="200"/>
-      <c r="AD9" s="167"/>
+      <c r="AC9" s="168"/>
+      <c r="AD9" s="192"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="11">
@@ -22449,10 +25042,10 @@
         <f t="shared" si="0"/>
         <v>1425</v>
       </c>
-      <c r="AC10" s="200">
+      <c r="AC10" s="168">
         <v>28225.5</v>
       </c>
-      <c r="AD10" s="167"/>
+      <c r="AD10" s="192"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="17">
@@ -22501,15 +25094,15 @@
         <f t="shared" si="0"/>
         <v>5638.53</v>
       </c>
-      <c r="AC11" s="200"/>
-      <c r="AD11" s="167"/>
-      <c r="AH11" s="168" t="s">
+      <c r="AC11" s="168"/>
+      <c r="AD11" s="192"/>
+      <c r="AH11" s="193" t="s">
         <v>83</v>
       </c>
-      <c r="AI11" s="168"/>
-      <c r="AJ11" s="168"/>
-      <c r="AK11" s="168"/>
-      <c r="AL11" s="168"/>
+      <c r="AI11" s="193"/>
+      <c r="AJ11" s="193"/>
+      <c r="AK11" s="193"/>
+      <c r="AL11" s="193"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="11">
@@ -22562,13 +25155,13 @@
         <f t="shared" si="0"/>
         <v>33365</v>
       </c>
-      <c r="AC12" s="200"/>
-      <c r="AD12" s="167"/>
-      <c r="AH12" s="168"/>
-      <c r="AI12" s="168"/>
-      <c r="AJ12" s="168"/>
-      <c r="AK12" s="168"/>
-      <c r="AL12" s="168"/>
+      <c r="AC12" s="168"/>
+      <c r="AD12" s="192"/>
+      <c r="AH12" s="193"/>
+      <c r="AI12" s="193"/>
+      <c r="AJ12" s="193"/>
+      <c r="AK12" s="193"/>
+      <c r="AL12" s="193"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="17">
@@ -22625,13 +25218,13 @@
         <f t="shared" si="0"/>
         <v>10965.96</v>
       </c>
-      <c r="AC13" s="200"/>
-      <c r="AD13" s="167"/>
-      <c r="AH13" s="168"/>
-      <c r="AI13" s="168"/>
-      <c r="AJ13" s="168"/>
-      <c r="AK13" s="168"/>
-      <c r="AL13" s="168"/>
+      <c r="AC13" s="168"/>
+      <c r="AD13" s="192"/>
+      <c r="AH13" s="193"/>
+      <c r="AI13" s="193"/>
+      <c r="AJ13" s="193"/>
+      <c r="AK13" s="193"/>
+      <c r="AL13" s="193"/>
     </row>
     <row r="14" spans="1:52" ht="18">
       <c r="A14" s="11">
@@ -22678,14 +25271,14 @@
         <f t="shared" si="0"/>
         <v>1614.53</v>
       </c>
-      <c r="AC14" s="200"/>
-      <c r="AD14" s="167"/>
-      <c r="AH14" s="164" t="s">
+      <c r="AC14" s="168"/>
+      <c r="AD14" s="192"/>
+      <c r="AH14" s="189" t="s">
         <v>62</v>
       </c>
-      <c r="AI14" s="164"/>
-      <c r="AJ14" s="164"/>
-      <c r="AK14" s="164"/>
+      <c r="AI14" s="189"/>
+      <c r="AJ14" s="189"/>
+      <c r="AK14" s="189"/>
       <c r="AL14" s="22">
         <f>AC4+AC19+AC23+AC10</f>
         <v>287751.42</v>
@@ -22742,14 +25335,14 @@
         <f t="shared" si="0"/>
         <v>6960.82</v>
       </c>
-      <c r="AC15" s="198"/>
-      <c r="AD15" s="167"/>
-      <c r="AH15" s="164" t="s">
+      <c r="AC15" s="166"/>
+      <c r="AD15" s="192"/>
+      <c r="AH15" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="AI15" s="164"/>
-      <c r="AJ15" s="164"/>
-      <c r="AK15" s="164"/>
+      <c r="AI15" s="189"/>
+      <c r="AJ15" s="189"/>
+      <c r="AK15" s="189"/>
       <c r="AL15" s="22">
         <f>AC20</f>
         <v>1000</v>
@@ -22800,16 +25393,16 @@
         <f t="shared" si="0"/>
         <v>3481.97</v>
       </c>
-      <c r="AC16" s="203">
+      <c r="AC16" s="170">
         <v>5000</v>
       </c>
-      <c r="AD16" s="167"/>
-      <c r="AH16" s="164" t="s">
+      <c r="AD16" s="192"/>
+      <c r="AH16" s="189" t="s">
         <v>63</v>
       </c>
-      <c r="AI16" s="164"/>
-      <c r="AJ16" s="164"/>
-      <c r="AK16" s="164"/>
+      <c r="AI16" s="189"/>
+      <c r="AJ16" s="189"/>
+      <c r="AK16" s="189"/>
       <c r="AL16" s="22">
         <f>AC16+AC28+AC34+AC35</f>
         <v>60000</v>
@@ -22866,24 +25459,24 @@
         <f>SUM(C17:AA17)</f>
         <v>5002</v>
       </c>
-      <c r="AC17" s="198"/>
-      <c r="AD17" s="167"/>
-      <c r="AH17" s="170" t="s">
+      <c r="AC17" s="166"/>
+      <c r="AD17" s="192"/>
+      <c r="AH17" s="201" t="s">
         <v>67</v>
       </c>
-      <c r="AI17" s="171"/>
-      <c r="AJ17" s="171"/>
-      <c r="AK17" s="172"/>
+      <c r="AI17" s="202"/>
+      <c r="AJ17" s="202"/>
+      <c r="AK17" s="203"/>
       <c r="AL17" s="22">
         <f>SUM(C37:K37)</f>
         <v>121331.08</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="19.5" customHeight="1">
-      <c r="A18" s="169" t="s">
+      <c r="A18" s="205" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="169"/>
+      <c r="B18" s="205"/>
       <c r="C18" s="23">
         <f>SUM(C4:C17)</f>
         <v>129.99</v>
@@ -22985,23 +25578,23 @@
         <v>0</v>
       </c>
       <c r="AB18" s="26">
-        <f t="shared" si="3"/>
-        <v>119520.64</v>
+        <f>SUM(AB4:AB17)</f>
+        <v>119520.64000000001</v>
       </c>
       <c r="AC18" s="27">
         <f t="shared" si="3"/>
         <v>118619.97</v>
       </c>
-      <c r="AD18" s="199">
+      <c r="AD18" s="167">
         <f>AC18-AB18</f>
-        <v>-900.67000000001303</v>
-      </c>
-      <c r="AH18" s="164" t="s">
+        <v>-900.67000000001281</v>
+      </c>
+      <c r="AH18" s="189" t="s">
         <v>84</v>
       </c>
-      <c r="AI18" s="164"/>
-      <c r="AJ18" s="164"/>
-      <c r="AK18" s="164"/>
+      <c r="AI18" s="189"/>
+      <c r="AJ18" s="189"/>
+      <c r="AK18" s="189"/>
       <c r="AL18" s="22">
         <f>SUM(L37:Q37)</f>
         <v>35695</v>
@@ -23055,13 +25648,13 @@
       <c r="AC19" s="16">
         <v>38575.449999999997</v>
       </c>
-      <c r="AD19" s="167"/>
-      <c r="AH19" s="164" t="s">
+      <c r="AD19" s="192"/>
+      <c r="AH19" s="189" t="s">
         <v>85</v>
       </c>
-      <c r="AI19" s="164"/>
-      <c r="AJ19" s="164"/>
-      <c r="AK19" s="164"/>
+      <c r="AI19" s="189"/>
+      <c r="AJ19" s="189"/>
+      <c r="AK19" s="189"/>
       <c r="AL19" s="22">
         <f>W37</f>
         <v>38934</v>
@@ -23118,14 +25711,14 @@
       <c r="AC20" s="21">
         <v>1000</v>
       </c>
-      <c r="AD20" s="167"/>
+      <c r="AD20" s="192"/>
       <c r="AF20" s="29"/>
-      <c r="AH20" s="164" t="s">
+      <c r="AH20" s="189" t="s">
         <v>86</v>
       </c>
-      <c r="AI20" s="164"/>
-      <c r="AJ20" s="164"/>
-      <c r="AK20" s="164"/>
+      <c r="AI20" s="189"/>
+      <c r="AJ20" s="189"/>
+      <c r="AK20" s="189"/>
       <c r="AL20" s="22">
         <f>SUM(U37:V37)</f>
         <v>15264.08</v>
@@ -23167,18 +25760,18 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="14"/>
       <c r="AB21" s="15">
-        <f t="shared" ref="AB21:AB35" si="4">SUM(C21:AA21)</f>
+        <f t="shared" ref="AB21:AB30" si="4">SUM(C21:AA21)</f>
         <v>1980</v>
       </c>
       <c r="AC21" s="21"/>
-      <c r="AD21" s="167"/>
-      <c r="AH21" s="164" t="s">
+      <c r="AD21" s="192"/>
+      <c r="AH21" s="207" t="s">
         <v>32</v>
       </c>
-      <c r="AI21" s="164"/>
-      <c r="AJ21" s="164"/>
-      <c r="AK21" s="164"/>
-      <c r="AL21" s="22">
+      <c r="AI21" s="207"/>
+      <c r="AJ21" s="207"/>
+      <c r="AK21" s="207"/>
+      <c r="AL21" s="208">
         <f>T37</f>
         <v>31093</v>
       </c>
@@ -23232,12 +25825,12 @@
         <v>3710.54</v>
       </c>
       <c r="AC22" s="21"/>
-      <c r="AD22" s="167"/>
-      <c r="AH22" s="164"/>
-      <c r="AI22" s="164"/>
-      <c r="AJ22" s="164"/>
-      <c r="AK22" s="164"/>
-      <c r="AL22" s="22"/>
+      <c r="AD22" s="192"/>
+      <c r="AH22" s="209"/>
+      <c r="AI22" s="209"/>
+      <c r="AJ22" s="209"/>
+      <c r="AK22" s="209"/>
+      <c r="AL22" s="210"/>
     </row>
     <row r="23" spans="1:38" ht="15.75">
       <c r="A23" s="11">
@@ -23288,7 +25881,7 @@
         <f>21986+70637+42933</f>
         <v>135556</v>
       </c>
-      <c r="AD23" s="167"/>
+      <c r="AD23" s="192"/>
     </row>
     <row r="24" spans="1:38" ht="15.75">
       <c r="A24" s="17">
@@ -23348,7 +25941,7 @@
         <v>26293.41</v>
       </c>
       <c r="AC24" s="21"/>
-      <c r="AD24" s="167"/>
+      <c r="AD24" s="192"/>
     </row>
     <row r="25" spans="1:38" ht="15.75">
       <c r="A25" s="11">
@@ -23393,7 +25986,7 @@
         <v>542</v>
       </c>
       <c r="AC25" s="16"/>
-      <c r="AD25" s="167"/>
+      <c r="AD25" s="192"/>
     </row>
     <row r="26" spans="1:38" ht="15.75">
       <c r="A26" s="17">
@@ -23453,7 +26046,7 @@
         <v>5856.07</v>
       </c>
       <c r="AC26" s="21"/>
-      <c r="AD26" s="167"/>
+      <c r="AD26" s="192"/>
     </row>
     <row r="27" spans="1:38" ht="15.75">
       <c r="A27" s="11">
@@ -23507,7 +26100,7 @@
         <v>14081.2</v>
       </c>
       <c r="AC27" s="21"/>
-      <c r="AD27" s="167"/>
+      <c r="AD27" s="192"/>
     </row>
     <row r="28" spans="1:38" ht="15.75">
       <c r="A28" s="17">
@@ -23551,7 +26144,7 @@
       <c r="AC28" s="21">
         <v>20000</v>
       </c>
-      <c r="AD28" s="167"/>
+      <c r="AD28" s="192"/>
     </row>
     <row r="29" spans="1:38" ht="15.75">
       <c r="A29" s="11">
@@ -23600,7 +26193,7 @@
         <v>4019.84</v>
       </c>
       <c r="AC29" s="21"/>
-      <c r="AD29" s="167"/>
+      <c r="AD29" s="192"/>
     </row>
     <row r="30" spans="1:38" ht="15.75">
       <c r="A30" s="17">
@@ -23651,182 +26244,182 @@
         <v>2628.39</v>
       </c>
       <c r="AC30" s="21"/>
-      <c r="AD30" s="167"/>
+      <c r="AD30" s="192"/>
     </row>
     <row r="31" spans="1:38" ht="16.5" thickBot="1">
-      <c r="A31" s="173">
+      <c r="A31" s="142">
         <v>30</v>
       </c>
-      <c r="B31" s="174" t="s">
+      <c r="B31" s="143" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="175"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="175">
+      <c r="C31" s="144"/>
+      <c r="D31" s="144"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="144">
         <f>586</f>
         <v>586</v>
       </c>
-      <c r="G31" s="175"/>
-      <c r="H31" s="175"/>
-      <c r="I31" s="175"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
-      <c r="L31" s="175"/>
-      <c r="M31" s="175"/>
-      <c r="N31" s="175"/>
-      <c r="O31" s="175">
+      <c r="G31" s="144"/>
+      <c r="H31" s="144"/>
+      <c r="I31" s="144"/>
+      <c r="J31" s="144"/>
+      <c r="K31" s="144"/>
+      <c r="L31" s="144"/>
+      <c r="M31" s="144"/>
+      <c r="N31" s="144"/>
+      <c r="O31" s="144">
         <v>1200</v>
       </c>
-      <c r="P31" s="175">
+      <c r="P31" s="144">
         <f>389</f>
         <v>389</v>
       </c>
-      <c r="Q31" s="175"/>
-      <c r="R31" s="175"/>
-      <c r="S31" s="175"/>
-      <c r="T31" s="175">
+      <c r="Q31" s="144"/>
+      <c r="R31" s="144"/>
+      <c r="S31" s="144"/>
+      <c r="T31" s="144">
         <f>5593</f>
         <v>5593</v>
       </c>
-      <c r="U31" s="175"/>
-      <c r="V31" s="175">
+      <c r="U31" s="144"/>
+      <c r="V31" s="144">
         <f>2124</f>
         <v>2124</v>
       </c>
-      <c r="W31" s="175">
+      <c r="W31" s="144">
         <f>1515+934+248</f>
         <v>2697</v>
       </c>
-      <c r="X31" s="175"/>
-      <c r="Y31" s="175"/>
-      <c r="Z31" s="175"/>
-      <c r="AA31" s="176"/>
+      <c r="X31" s="144"/>
+      <c r="Y31" s="144"/>
+      <c r="Z31" s="144"/>
+      <c r="AA31" s="145"/>
       <c r="AB31" s="15">
         <f>SUM(C31:AA31)</f>
         <v>12589</v>
       </c>
       <c r="AC31" s="21"/>
-      <c r="AD31" s="167"/>
+      <c r="AD31" s="192"/>
     </row>
     <row r="32" spans="1:38" ht="15.75">
-      <c r="A32" s="182">
+      <c r="A32" s="150">
         <v>1</v>
       </c>
-      <c r="B32" s="183" t="s">
+      <c r="B32" s="151" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="184"/>
-      <c r="D32" s="184"/>
-      <c r="E32" s="184"/>
-      <c r="F32" s="184">
+      <c r="C32" s="152"/>
+      <c r="D32" s="152"/>
+      <c r="E32" s="152"/>
+      <c r="F32" s="152">
         <v>2323.1</v>
       </c>
-      <c r="G32" s="184"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="184">
+      <c r="G32" s="152"/>
+      <c r="H32" s="152"/>
+      <c r="I32" s="152">
         <f>4290+463.32</f>
         <v>4753.32</v>
       </c>
-      <c r="J32" s="184">
+      <c r="J32" s="152">
         <f>1360</f>
         <v>1360</v>
       </c>
-      <c r="K32" s="184">
+      <c r="K32" s="152">
         <f>980</f>
         <v>980</v>
       </c>
-      <c r="L32" s="184"/>
-      <c r="M32" s="184"/>
-      <c r="N32" s="184"/>
-      <c r="O32" s="184">
+      <c r="L32" s="152"/>
+      <c r="M32" s="152"/>
+      <c r="N32" s="152"/>
+      <c r="O32" s="152">
         <f>300</f>
         <v>300</v>
       </c>
-      <c r="P32" s="184"/>
-      <c r="Q32" s="184"/>
-      <c r="R32" s="184"/>
-      <c r="S32" s="184"/>
-      <c r="T32" s="184"/>
-      <c r="U32" s="184">
+      <c r="P32" s="152"/>
+      <c r="Q32" s="152"/>
+      <c r="R32" s="152"/>
+      <c r="S32" s="152"/>
+      <c r="T32" s="152"/>
+      <c r="U32" s="152">
         <f>337</f>
         <v>337</v>
       </c>
-      <c r="V32" s="184"/>
-      <c r="W32" s="184">
+      <c r="V32" s="152"/>
+      <c r="W32" s="152">
         <f>1289+1202</f>
         <v>2491</v>
       </c>
-      <c r="X32" s="184"/>
-      <c r="Y32" s="184"/>
-      <c r="Z32" s="184">
+      <c r="X32" s="152"/>
+      <c r="Y32" s="152"/>
+      <c r="Z32" s="152">
         <f>6000</f>
         <v>6000</v>
       </c>
-      <c r="AA32" s="185"/>
+      <c r="AA32" s="153"/>
       <c r="AB32" s="15">
         <f t="shared" ref="AB32:AB35" si="5">SUM(C32:AA32)</f>
         <v>18544.419999999998</v>
       </c>
       <c r="AC32" s="21"/>
-      <c r="AD32" s="167"/>
+      <c r="AD32" s="192"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
-      <c r="A33" s="189">
+      <c r="A33" s="157">
         <v>2</v>
       </c>
-      <c r="B33" s="190" t="s">
+      <c r="B33" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="191"/>
-      <c r="D33" s="191"/>
-      <c r="E33" s="191"/>
-      <c r="F33" s="191"/>
-      <c r="G33" s="191"/>
-      <c r="H33" s="191"/>
-      <c r="I33" s="191">
+      <c r="C33" s="159"/>
+      <c r="D33" s="159"/>
+      <c r="E33" s="159"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="159"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="159">
         <f>2839+4140+447.12</f>
         <v>7426.12</v>
       </c>
-      <c r="J33" s="191"/>
-      <c r="K33" s="191"/>
-      <c r="L33" s="191"/>
-      <c r="M33" s="191"/>
-      <c r="N33" s="191">
+      <c r="J33" s="159"/>
+      <c r="K33" s="159"/>
+      <c r="L33" s="159"/>
+      <c r="M33" s="159"/>
+      <c r="N33" s="159">
         <f>399</f>
         <v>399</v>
       </c>
-      <c r="O33" s="191"/>
-      <c r="P33" s="191"/>
-      <c r="Q33" s="191"/>
-      <c r="R33" s="191">
+      <c r="O33" s="159"/>
+      <c r="P33" s="159"/>
+      <c r="Q33" s="159"/>
+      <c r="R33" s="159">
         <f>1510.97</f>
         <v>1510.97</v>
       </c>
-      <c r="S33" s="191"/>
-      <c r="T33" s="191"/>
-      <c r="U33" s="191">
+      <c r="S33" s="159"/>
+      <c r="T33" s="159"/>
+      <c r="U33" s="159">
         <f>95+95</f>
         <v>190</v>
       </c>
-      <c r="V33" s="191"/>
-      <c r="W33" s="191"/>
-      <c r="X33" s="191"/>
-      <c r="Y33" s="191"/>
-      <c r="Z33" s="191"/>
-      <c r="AA33" s="192"/>
+      <c r="V33" s="159"/>
+      <c r="W33" s="159"/>
+      <c r="X33" s="159"/>
+      <c r="Y33" s="159"/>
+      <c r="Z33" s="159"/>
+      <c r="AA33" s="160"/>
       <c r="AB33" s="15">
         <f t="shared" si="5"/>
         <v>9526.09</v>
       </c>
       <c r="AC33" s="21"/>
-      <c r="AD33" s="167"/>
+      <c r="AD33" s="192"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
-      <c r="A34" s="186">
+      <c r="A34" s="154">
         <v>3</v>
       </c>
-      <c r="B34" s="187" t="s">
+      <c r="B34" s="155" t="s">
         <v>45</v>
       </c>
       <c r="C34" s="50"/>
@@ -23874,7 +26467,7 @@
         <f>1700</f>
         <v>1700</v>
       </c>
-      <c r="AA34" s="188"/>
+      <c r="AA34" s="156"/>
       <c r="AB34" s="15">
         <f t="shared" si="5"/>
         <v>22952</v>
@@ -23882,55 +26475,55 @@
       <c r="AC34" s="37">
         <v>20000</v>
       </c>
-      <c r="AD34" s="167"/>
+      <c r="AD34" s="192"/>
     </row>
     <row r="35" spans="1:34" ht="16.5" thickBot="1">
-      <c r="A35" s="193">
+      <c r="A35" s="161">
         <v>4</v>
       </c>
-      <c r="B35" s="194" t="s">
+      <c r="B35" s="162" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="195"/>
-      <c r="D35" s="195"/>
-      <c r="E35" s="195"/>
-      <c r="F35" s="195"/>
-      <c r="G35" s="195"/>
-      <c r="H35" s="195"/>
-      <c r="I35" s="195">
+      <c r="C35" s="163"/>
+      <c r="D35" s="163"/>
+      <c r="E35" s="163"/>
+      <c r="F35" s="163"/>
+      <c r="G35" s="163"/>
+      <c r="H35" s="163"/>
+      <c r="I35" s="163">
         <f>5900+651+13880+1508</f>
         <v>21939</v>
       </c>
-      <c r="J35" s="195"/>
-      <c r="K35" s="195"/>
-      <c r="L35" s="195"/>
-      <c r="M35" s="195"/>
-      <c r="N35" s="195">
+      <c r="J35" s="163"/>
+      <c r="K35" s="163"/>
+      <c r="L35" s="163"/>
+      <c r="M35" s="163"/>
+      <c r="N35" s="163">
         <f>300</f>
         <v>300</v>
       </c>
-      <c r="O35" s="195"/>
-      <c r="P35" s="195"/>
-      <c r="Q35" s="195"/>
-      <c r="R35" s="195"/>
-      <c r="S35" s="195"/>
-      <c r="T35" s="195"/>
-      <c r="U35" s="195">
+      <c r="O35" s="163"/>
+      <c r="P35" s="163"/>
+      <c r="Q35" s="163"/>
+      <c r="R35" s="163"/>
+      <c r="S35" s="163"/>
+      <c r="T35" s="163"/>
+      <c r="U35" s="163">
         <f>423+526+838</f>
         <v>1787</v>
       </c>
-      <c r="V35" s="195"/>
-      <c r="W35" s="195"/>
-      <c r="X35" s="195">
+      <c r="V35" s="163"/>
+      <c r="W35" s="163"/>
+      <c r="X35" s="163">
         <f>375</f>
         <v>375</v>
       </c>
-      <c r="Y35" s="195"/>
-      <c r="Z35" s="195">
+      <c r="Y35" s="163"/>
+      <c r="Z35" s="163">
         <f>1400</f>
         <v>1400</v>
       </c>
-      <c r="AA35" s="196"/>
+      <c r="AA35" s="164"/>
       <c r="AB35" s="15">
         <f t="shared" si="5"/>
         <v>25801</v>
@@ -23938,115 +26531,115 @@
       <c r="AC35" s="37">
         <v>15000</v>
       </c>
-      <c r="AD35" s="167"/>
+      <c r="AD35" s="192"/>
     </row>
     <row r="36" spans="1:34" ht="24" customHeight="1">
-      <c r="A36" s="177" t="s">
+      <c r="A36" s="204" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="177"/>
-      <c r="C36" s="178">
+      <c r="B36" s="204"/>
+      <c r="C36" s="146">
         <f t="shared" ref="C36:AC36" si="6">SUM(C19:C35)</f>
         <v>1293.0899999999999</v>
       </c>
-      <c r="D36" s="178">
+      <c r="D36" s="146">
         <f t="shared" si="6"/>
         <v>2055.8000000000002</v>
       </c>
-      <c r="E36" s="178">
+      <c r="E36" s="146">
         <f t="shared" si="6"/>
         <v>3550.01</v>
       </c>
-      <c r="F36" s="178">
+      <c r="F36" s="146">
         <f t="shared" si="6"/>
         <v>7603.8099999999995</v>
       </c>
-      <c r="G36" s="178">
+      <c r="G36" s="146">
         <f t="shared" si="6"/>
         <v>926</v>
       </c>
-      <c r="H36" s="178">
+      <c r="H36" s="146">
         <f t="shared" si="6"/>
         <v>9215</v>
       </c>
-      <c r="I36" s="178">
+      <c r="I36" s="146">
         <f t="shared" si="6"/>
         <v>49258.44</v>
       </c>
-      <c r="J36" s="178">
+      <c r="J36" s="146">
         <f t="shared" si="6"/>
         <v>6442</v>
       </c>
-      <c r="K36" s="178">
+      <c r="K36" s="146">
         <f t="shared" si="6"/>
         <v>4820</v>
       </c>
-      <c r="L36" s="179">
+      <c r="L36" s="147">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M36" s="179">
+      <c r="M36" s="147">
         <f t="shared" si="6"/>
         <v>5345</v>
       </c>
-      <c r="N36" s="179">
+      <c r="N36" s="147">
         <f t="shared" si="6"/>
         <v>1747</v>
       </c>
-      <c r="O36" s="179">
+      <c r="O36" s="147">
         <f t="shared" si="6"/>
         <v>1500</v>
       </c>
-      <c r="P36" s="179">
+      <c r="P36" s="147">
         <f t="shared" si="6"/>
         <v>389</v>
       </c>
-      <c r="Q36" s="179">
+      <c r="Q36" s="147">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R36" s="180">
+      <c r="R36" s="148">
         <f t="shared" si="6"/>
         <v>6339.95</v>
       </c>
-      <c r="S36" s="180">
+      <c r="S36" s="148">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T36" s="180">
+      <c r="T36" s="148">
         <f t="shared" si="6"/>
         <v>11703</v>
       </c>
-      <c r="U36" s="180">
+      <c r="U36" s="148">
         <f t="shared" si="6"/>
         <v>3897</v>
       </c>
-      <c r="V36" s="180">
+      <c r="V36" s="148">
         <f t="shared" si="6"/>
         <v>5937.3499999999995</v>
       </c>
-      <c r="W36" s="180">
+      <c r="W36" s="148">
         <f t="shared" si="6"/>
         <v>18675</v>
       </c>
-      <c r="X36" s="180">
+      <c r="X36" s="148">
         <f t="shared" si="6"/>
         <v>4949</v>
       </c>
-      <c r="Y36" s="180">
+      <c r="Y36" s="148">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="180">
+      <c r="Z36" s="148">
         <f t="shared" si="6"/>
         <v>9100</v>
       </c>
-      <c r="AA36" s="181">
+      <c r="AA36" s="149">
         <f t="shared" si="6"/>
         <v>73610.12</v>
       </c>
       <c r="AB36" s="26">
-        <f t="shared" si="6"/>
+        <f>SUM(AB19:AB35)</f>
         <v>228356.57000000004</v>
       </c>
       <c r="AC36" s="27">
@@ -24057,13 +26650,13 @@
         <f>AC36-AB36</f>
         <v>1774.8799999999756</v>
       </c>
-      <c r="AH36" s="197"/>
+      <c r="AH36" s="165"/>
     </row>
     <row r="37" spans="1:34" ht="31.5" customHeight="1">
-      <c r="A37" s="166" t="s">
+      <c r="A37" s="191" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="166"/>
+      <c r="B37" s="191"/>
       <c r="C37" s="31">
         <f t="shared" ref="C37:R37" si="7">SUM(C18,C36)</f>
         <v>1423.08</v>
@@ -24130,7 +26723,7 @@
       </c>
       <c r="S37" s="31"/>
       <c r="T37" s="31">
-        <f t="shared" ref="T37:AD37" si="8">SUM(T18,T36)</f>
+        <f t="shared" ref="T37:AC37" si="8">SUM(T18,T36)</f>
         <v>31093</v>
       </c>
       <c r="U37" s="31">
@@ -24163,15 +26756,15 @@
       </c>
       <c r="AB37" s="33">
         <f t="shared" si="8"/>
-        <v>347877.21</v>
+        <v>347877.21000000008</v>
       </c>
       <c r="AC37" s="34">
         <f t="shared" si="8"/>
         <v>348751.42000000004</v>
       </c>
-      <c r="AD37" s="202">
+      <c r="AD37" s="169">
         <f>SUM(AD18,AD36)</f>
-        <v>874.20999999996252</v>
+        <v>874.20999999996275</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -24194,6 +26787,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="AD19:AD35"/>
     <mergeCell ref="AH11:AL13"/>
@@ -24209,12 +26808,6 @@
     <mergeCell ref="AH16:AK16"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="AH18:AK18"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
